--- a/sgzzlb.xlsx
+++ b/sgzzlb.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piece\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02_SourceCode\sgzzlb_tech_tree\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="304">
   <si>
     <t>장</t>
   </si>
@@ -981,6 +981,38 @@
   </si>
   <si>
     <t>최대 자원 +3000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 자원 +250000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 자원 +300000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 자원 +350000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>군사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>군사부</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1092,7 +1124,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1120,6 +1152,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1230,7 +1280,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1296,13 +1346,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="11" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1318,6 +1361,22 @@
     <xf numFmtId="3" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1602,34 +1661,40 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:EL58"/>
+  <dimension ref="A1:EQ58"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="16" customWidth="1"/>
+    <col min="2" max="2" width="7.5" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="6.625" style="16" customWidth="1"/>
     <col min="5" max="5" width="7.875" style="16" customWidth="1"/>
     <col min="6" max="6" width="1.625" style="27" customWidth="1"/>
-    <col min="7" max="7" width="5.75" style="16" customWidth="1"/>
+    <col min="7" max="7" width="7.5" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="6.625" style="16" customWidth="1"/>
-    <col min="11" max="11" width="15.25" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.25" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.625" style="27" customWidth="1"/>
-    <col min="13" max="16" width="6.625" style="16" customWidth="1"/>
-    <col min="17" max="17" width="16" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="6.625" style="16" customWidth="1"/>
+    <col min="17" max="17" width="16" style="31" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="1.625" style="27" customWidth="1"/>
-    <col min="19" max="22" width="6.625" style="16" customWidth="1"/>
-    <col min="23" max="23" width="16" style="36" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="6.625" style="16" customWidth="1"/>
+    <col min="23" max="23" width="16" style="31" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="1.625" style="27" customWidth="1"/>
-    <col min="25" max="28" width="6.625" style="16" customWidth="1"/>
-    <col min="29" max="29" width="16" style="36" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="6.625" style="16" customWidth="1"/>
+    <col min="29" max="29" width="16" style="31" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="1.625" style="27" customWidth="1"/>
-    <col min="31" max="34" width="6.625" style="16" customWidth="1"/>
-    <col min="35" max="35" width="16" style="36" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="6.625" style="16" customWidth="1"/>
+    <col min="35" max="35" width="16" style="31" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="1.625" style="27" customWidth="1"/>
-    <col min="37" max="40" width="7" style="16" customWidth="1"/>
+    <col min="37" max="37" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="7" style="16" customWidth="1"/>
     <col min="41" max="41" width="1.625" style="27" customWidth="1"/>
-    <col min="42" max="45" width="7" style="16" customWidth="1"/>
-    <col min="46" max="46" width="14" style="36" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="43" max="45" width="7" style="16" customWidth="1"/>
+    <col min="46" max="46" width="14" style="31" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="1.625" style="27" customWidth="1"/>
     <col min="48" max="48" width="9.625" style="16" customWidth="1"/>
     <col min="49" max="51" width="7" style="16" customWidth="1"/>
@@ -1638,16 +1703,16 @@
     <col min="54" max="54" width="9.625" style="16" customWidth="1"/>
     <col min="55" max="57" width="7" style="16" customWidth="1"/>
     <col min="58" max="58" width="1.625" style="27" customWidth="1"/>
-    <col min="59" max="59" width="5.5" style="16" customWidth="1"/>
-    <col min="60" max="61" width="7" style="16" customWidth="1"/>
-    <col min="62" max="62" width="8.375" style="16" customWidth="1"/>
+    <col min="59" max="59" width="9.625" style="16" customWidth="1"/>
+    <col min="60" max="62" width="7" style="16" customWidth="1"/>
     <col min="63" max="63" width="1.625" style="27" customWidth="1"/>
     <col min="64" max="64" width="5.5" style="16" customWidth="1"/>
     <col min="65" max="66" width="7" style="16" customWidth="1"/>
     <col min="67" max="67" width="8.375" style="16" customWidth="1"/>
     <col min="68" max="68" width="1.625" style="27" customWidth="1"/>
-    <col min="69" max="69" width="9.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="70" max="72" width="7" style="16" customWidth="1"/>
+    <col min="69" max="69" width="5.5" style="16" customWidth="1"/>
+    <col min="70" max="71" width="7" style="16" customWidth="1"/>
+    <col min="72" max="72" width="8.375" style="16" customWidth="1"/>
     <col min="73" max="73" width="1.625" style="27" customWidth="1"/>
     <col min="74" max="74" width="9.625" style="16" bestFit="1" customWidth="1"/>
     <col min="75" max="77" width="7" style="16" customWidth="1"/>
@@ -1659,9 +1724,9 @@
     <col min="85" max="87" width="7" style="16" customWidth="1"/>
     <col min="88" max="88" width="1.625" style="27" customWidth="1"/>
     <col min="89" max="89" width="9.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="90" max="92" width="7.875" style="16" customWidth="1"/>
+    <col min="90" max="92" width="7" style="16" customWidth="1"/>
     <col min="93" max="93" width="1.625" style="27" customWidth="1"/>
-    <col min="94" max="94" width="8.125" style="16" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="9.625" style="16" bestFit="1" customWidth="1"/>
     <col min="95" max="97" width="7.875" style="16" customWidth="1"/>
     <col min="98" max="98" width="1.625" style="27" customWidth="1"/>
     <col min="99" max="99" width="8.125" style="16" bestFit="1" customWidth="1"/>
@@ -1673,404 +1738,590 @@
     <col min="109" max="109" width="8.125" style="16" bestFit="1" customWidth="1"/>
     <col min="110" max="112" width="7.875" style="16" customWidth="1"/>
     <col min="113" max="113" width="1.625" style="27" customWidth="1"/>
-    <col min="114" max="114" width="6" style="16" bestFit="1" customWidth="1"/>
-    <col min="115" max="117" width="6.625" style="16" customWidth="1"/>
+    <col min="114" max="114" width="8.125" style="16" bestFit="1" customWidth="1"/>
+    <col min="115" max="117" width="7.875" style="16" customWidth="1"/>
     <col min="118" max="118" width="1.625" style="27" customWidth="1"/>
-    <col min="119" max="119" width="6" style="16" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="7.5" style="16" bestFit="1" customWidth="1"/>
     <col min="120" max="122" width="6.625" style="16" customWidth="1"/>
     <col min="123" max="123" width="1.625" style="27" customWidth="1"/>
-    <col min="124" max="124" width="6" style="16" bestFit="1" customWidth="1"/>
-    <col min="125" max="126" width="6.625" style="16" customWidth="1"/>
-    <col min="127" max="127" width="7.875" style="16" customWidth="1"/>
+    <col min="124" max="124" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="125" max="127" width="6.625" style="16" customWidth="1"/>
     <col min="128" max="128" width="1.625" style="27" customWidth="1"/>
-    <col min="129" max="129" width="6" style="16" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="7.5" style="16" bestFit="1" customWidth="1"/>
     <col min="130" max="131" width="6.625" style="16" customWidth="1"/>
     <col min="132" max="132" width="7.875" style="16" customWidth="1"/>
     <col min="133" max="133" width="1.625" style="27" customWidth="1"/>
-    <col min="134" max="134" width="4.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="7.5" style="16" bestFit="1" customWidth="1"/>
     <col min="135" max="136" width="6.625" style="16" customWidth="1"/>
     <col min="137" max="137" width="7.875" style="16" customWidth="1"/>
     <col min="138" max="138" width="1.625" style="27" customWidth="1"/>
-    <col min="139" max="139" width="6" style="16" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="7.5" style="16" bestFit="1" customWidth="1"/>
     <col min="140" max="141" width="6.625" style="16" customWidth="1"/>
     <col min="142" max="142" width="7.875" style="16" customWidth="1"/>
-    <col min="143" max="143" width="6.625" style="16" customWidth="1"/>
-    <col min="144" max="16384" width="12.625" style="16"/>
+    <col min="143" max="143" width="1.625" style="27" customWidth="1"/>
+    <col min="144" max="144" width="7.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="145" max="146" width="6.625" style="16" customWidth="1"/>
+    <col min="147" max="147" width="7.875" style="16" customWidth="1"/>
+    <col min="148" max="148" width="6.625" style="16" customWidth="1"/>
+    <col min="149" max="16384" width="12.625" style="16"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:142" ht="15.75" customHeight="1">
-      <c r="B2" s="37" t="s">
+    <row r="1" spans="2:147" ht="15.75" customHeight="1">
+      <c r="B1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="N1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="S1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="T1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="AE1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="AF1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="AK1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="AL1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="AP1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="AQ1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="AV1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="AW1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="BB1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="BC1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="BG1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="BH1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="BL1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="BM1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="BQ1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="BR1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="BV1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="BW1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="CA1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="CB1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="CF1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="CG1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="CK1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="CL1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="CP1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="CQ1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="CU1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="CV1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="CZ1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="DA1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="DE1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="DF1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="DJ1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="DK1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="DO1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="DP1" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="DT1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="DU1" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="DY1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="DZ1" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="ED1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="EE1" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="EI1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="EJ1" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="EN1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="EO1" s="38" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="2:147" ht="15.75" customHeight="1">
+      <c r="B2" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="32" t="s">
         <v>117</v>
       </c>
       <c r="L2" s="28"/>
-      <c r="M2" s="37" t="s">
+      <c r="M2" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="N2" s="37" t="s">
+      <c r="N2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="37" t="s">
+      <c r="O2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="37" t="s">
+      <c r="P2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="37" t="s">
+      <c r="Q2" s="32" t="s">
         <v>116</v>
       </c>
       <c r="R2" s="25"/>
-      <c r="S2" s="37" t="s">
+      <c r="S2" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="T2" s="37" t="s">
+      <c r="T2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="37" t="s">
+      <c r="U2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="V2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="37" t="s">
+      <c r="W2" s="32" t="s">
         <v>116</v>
       </c>
       <c r="X2" s="25"/>
-      <c r="Y2" s="37" t="s">
+      <c r="Y2" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="Z2" s="37" t="s">
+      <c r="Z2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="AA2" s="37" t="s">
+      <c r="AA2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="37" t="s">
+      <c r="AB2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="AC2" s="37" t="s">
+      <c r="AC2" s="32" t="s">
         <v>116</v>
       </c>
       <c r="AD2" s="25"/>
-      <c r="AE2" s="37" t="s">
+      <c r="AE2" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="AF2" s="37" t="s">
+      <c r="AF2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="AG2" s="37" t="s">
+      <c r="AG2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="AH2" s="37" t="s">
+      <c r="AH2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="AI2" s="37" t="s">
+      <c r="AI2" s="32" t="s">
         <v>116</v>
       </c>
       <c r="AJ2" s="25"/>
-      <c r="AK2" s="37" t="s">
+      <c r="AK2" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="AL2" s="37" t="s">
+      <c r="AL2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="AM2" s="37" t="s">
+      <c r="AM2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="AN2" s="37" t="s">
+      <c r="AN2" s="32" t="s">
         <v>5</v>
       </c>
       <c r="AO2" s="25"/>
-      <c r="AP2" s="37" t="s">
+      <c r="AP2" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="AQ2" s="37" t="s">
+      <c r="AQ2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="AR2" s="37" t="s">
+      <c r="AR2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="AS2" s="37" t="s">
+      <c r="AS2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="AT2" s="37" t="s">
+      <c r="AT2" s="32" t="s">
         <v>116</v>
       </c>
       <c r="AU2" s="25"/>
-      <c r="AV2" s="37" t="s">
+      <c r="AV2" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="AW2" s="37" t="s">
+      <c r="AW2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="AX2" s="37" t="s">
+      <c r="AX2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="AY2" s="37" t="s">
+      <c r="AY2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="AZ2" s="37" t="s">
+      <c r="AZ2" s="32" t="s">
         <v>116</v>
       </c>
       <c r="BA2" s="25"/>
-      <c r="BB2" s="40" t="s">
+      <c r="BB2" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="BC2" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="BD2" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE2" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF2" s="25"/>
+      <c r="BG2" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="BC2" s="40" t="s">
+      <c r="BH2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="BD2" s="40" t="s">
+      <c r="BI2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="BE2" s="40" t="s">
+      <c r="BJ2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="BF2" s="25"/>
-      <c r="BG2" s="37" t="s">
+      <c r="BK2" s="25"/>
+      <c r="BL2" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" s="37" t="s">
+      <c r="BM2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="BI2" s="37" t="s">
+      <c r="BN2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="BJ2" s="37" t="s">
+      <c r="BO2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="BK2" s="25"/>
-      <c r="BL2" s="37" t="s">
+      <c r="BP2" s="25"/>
+      <c r="BQ2" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="BM2" s="37" t="s">
+      <c r="BR2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="BN2" s="37" t="s">
+      <c r="BS2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="BO2" s="37" t="s">
+      <c r="BT2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="BP2" s="25"/>
-      <c r="BQ2" s="40" t="s">
+      <c r="BU2" s="25"/>
+      <c r="BV2" s="35" t="s">
         <v>241</v>
       </c>
-      <c r="BR2" s="40" t="s">
+      <c r="BW2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="BS2" s="40" t="s">
+      <c r="BX2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="BT2" s="40" t="s">
+      <c r="BY2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="BU2" s="25"/>
-      <c r="BV2" s="40" t="s">
+      <c r="BZ2" s="25"/>
+      <c r="CA2" s="35" t="s">
         <v>240</v>
       </c>
-      <c r="BW2" s="40" t="s">
+      <c r="CB2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="BX2" s="40" t="s">
+      <c r="CC2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="BY2" s="40" t="s">
+      <c r="CD2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="BZ2" s="25"/>
-      <c r="CA2" s="40" t="s">
+      <c r="CE2" s="25"/>
+      <c r="CF2" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="CB2" s="40" t="s">
+      <c r="CG2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="CC2" s="40" t="s">
+      <c r="CH2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="CD2" s="40" t="s">
+      <c r="CI2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="CE2" s="25"/>
-      <c r="CF2" s="40" t="s">
+      <c r="CJ2" s="25"/>
+      <c r="CK2" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="CG2" s="40" t="s">
+      <c r="CL2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="CH2" s="40" t="s">
+      <c r="CM2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="CI2" s="40" t="s">
+      <c r="CN2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="CJ2" s="25"/>
-      <c r="CK2" s="40" t="s">
+      <c r="CO2" s="25"/>
+      <c r="CP2" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="CL2" s="40" t="s">
+      <c r="CQ2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="CM2" s="40" t="s">
+      <c r="CR2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="CN2" s="40" t="s">
+      <c r="CS2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="CO2" s="25"/>
-      <c r="CP2" s="40" t="s">
+      <c r="CT2" s="25"/>
+      <c r="CU2" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="CQ2" s="40" t="s">
+      <c r="CV2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="CR2" s="40" t="s">
+      <c r="CW2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="CS2" s="40" t="s">
+      <c r="CX2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="CT2" s="25"/>
-      <c r="CU2" s="40" t="s">
+      <c r="CY2" s="25"/>
+      <c r="CZ2" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="CV2" s="40" t="s">
+      <c r="DA2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="CW2" s="40" t="s">
+      <c r="DB2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="CX2" s="40" t="s">
+      <c r="DC2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="CY2" s="25"/>
-      <c r="CZ2" s="40" t="s">
+      <c r="DD2" s="25"/>
+      <c r="DE2" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="DA2" s="40" t="s">
+      <c r="DF2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="DB2" s="40" t="s">
+      <c r="DG2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="DC2" s="40" t="s">
+      <c r="DH2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="DD2" s="25"/>
-      <c r="DE2" s="40" t="s">
+      <c r="DI2" s="25"/>
+      <c r="DJ2" s="35" t="s">
         <v>248</v>
       </c>
-      <c r="DF2" s="40" t="s">
+      <c r="DK2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="DG2" s="40" t="s">
+      <c r="DL2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="DH2" s="40" t="s">
+      <c r="DM2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="DI2" s="25"/>
-      <c r="DJ2" s="40" t="s">
+      <c r="DN2" s="25"/>
+      <c r="DO2" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="DK2" s="40" t="s">
+      <c r="DP2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="DL2" s="40" t="s">
+      <c r="DQ2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="DM2" s="40" t="s">
+      <c r="DR2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="DN2" s="25"/>
-      <c r="DO2" s="40" t="s">
+      <c r="DS2" s="25"/>
+      <c r="DT2" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="DP2" s="40" t="s">
+      <c r="DU2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="DQ2" s="40" t="s">
+      <c r="DV2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="DR2" s="40" t="s">
+      <c r="DW2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="DS2" s="25"/>
-      <c r="DT2" s="40" t="s">
+      <c r="DX2" s="25"/>
+      <c r="DY2" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="DU2" s="40" t="s">
+      <c r="DZ2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="DV2" s="40" t="s">
+      <c r="EA2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="DW2" s="40" t="s">
+      <c r="EB2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="DX2" s="25"/>
-      <c r="DY2" s="40" t="s">
+      <c r="EC2" s="25"/>
+      <c r="ED2" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="DZ2" s="40" t="s">
+      <c r="EE2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="EA2" s="40" t="s">
+      <c r="EF2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="EB2" s="40" t="s">
+      <c r="EG2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="EC2" s="25"/>
-      <c r="ED2" s="37" t="s">
+      <c r="EH2" s="25"/>
+      <c r="EI2" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="EE2" s="37" t="s">
+      <c r="EJ2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="EF2" s="37" t="s">
+      <c r="EK2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="EG2" s="37" t="s">
+      <c r="EL2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="EH2" s="25"/>
-      <c r="EI2" s="40" t="s">
+      <c r="EM2" s="25"/>
+      <c r="EN2" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="EJ2" s="40" t="s">
+      <c r="EO2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="EK2" s="40" t="s">
+      <c r="EP2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="EL2" s="40" t="s">
+      <c r="EQ2" s="35" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:142" ht="15.75" customHeight="1">
+    <row r="3" spans="2:147" ht="15.75" customHeight="1">
       <c r="B3" s="20">
         <v>1</v>
       </c>
@@ -2207,52 +2458,52 @@
         <v>1</v>
       </c>
       <c r="BC3" s="21">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="BD3" s="21">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="BE3" s="21">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="BF3" s="26"/>
       <c r="BG3" s="20">
         <v>1</v>
       </c>
       <c r="BH3" s="21">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="BI3" s="21">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="BJ3" s="21">
-        <v>2000</v>
+        <v>150000</v>
       </c>
       <c r="BK3" s="26"/>
       <c r="BL3" s="20">
         <v>1</v>
       </c>
       <c r="BM3" s="21">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="BN3" s="21">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="BO3" s="21">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="BP3" s="26"/>
       <c r="BQ3" s="20">
         <v>1</v>
       </c>
       <c r="BR3" s="21">
-        <v>1600</v>
+        <v>6000</v>
       </c>
       <c r="BS3" s="21">
-        <v>3200</v>
+        <v>6000</v>
       </c>
       <c r="BT3" s="21">
-        <v>3200</v>
+        <v>8000</v>
       </c>
       <c r="BU3" s="26"/>
       <c r="BV3" s="20">
@@ -2272,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="CB3" s="21">
+        <v>1600</v>
+      </c>
+      <c r="CC3" s="21">
         <v>3200</v>
-      </c>
-      <c r="CC3" s="21">
-        <v>1600</v>
       </c>
       <c r="CD3" s="21">
         <v>3200</v>
@@ -2298,23 +2549,23 @@
         <v>1</v>
       </c>
       <c r="CL3" s="21">
-        <v>40000</v>
+        <v>3200</v>
       </c>
       <c r="CM3" s="21">
-        <v>20000</v>
+        <v>1600</v>
       </c>
       <c r="CN3" s="21">
-        <v>40000</v>
+        <v>3200</v>
       </c>
       <c r="CO3" s="26"/>
       <c r="CP3" s="20">
         <v>1</v>
       </c>
       <c r="CQ3" s="21">
+        <v>40000</v>
+      </c>
+      <c r="CR3" s="21">
         <v>20000</v>
-      </c>
-      <c r="CR3" s="21">
-        <v>40000</v>
       </c>
       <c r="CS3" s="21">
         <v>40000</v>
@@ -2324,10 +2575,10 @@
         <v>1</v>
       </c>
       <c r="CV3" s="21">
+        <v>20000</v>
+      </c>
+      <c r="CW3" s="21">
         <v>40000</v>
-      </c>
-      <c r="CW3" s="21">
-        <v>20000</v>
       </c>
       <c r="CX3" s="21">
         <v>40000</v>
@@ -2337,10 +2588,10 @@
         <v>1</v>
       </c>
       <c r="DA3" s="21">
+        <v>40000</v>
+      </c>
+      <c r="DB3" s="21">
         <v>20000</v>
-      </c>
-      <c r="DB3" s="21">
-        <v>40000</v>
       </c>
       <c r="DC3" s="21">
         <v>40000</v>
@@ -2350,10 +2601,10 @@
         <v>1</v>
       </c>
       <c r="DF3" s="21">
+        <v>20000</v>
+      </c>
+      <c r="DG3" s="21">
         <v>40000</v>
-      </c>
-      <c r="DG3" s="21">
-        <v>20000</v>
       </c>
       <c r="DH3" s="21">
         <v>40000</v>
@@ -2363,23 +2614,23 @@
         <v>1</v>
       </c>
       <c r="DK3" s="21">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="DL3" s="21">
-        <v>32000</v>
+        <v>20000</v>
       </c>
       <c r="DM3" s="21">
-        <v>32000</v>
+        <v>40000</v>
       </c>
       <c r="DN3" s="26"/>
       <c r="DO3" s="20">
         <v>1</v>
       </c>
       <c r="DP3" s="21">
+        <v>16000</v>
+      </c>
+      <c r="DQ3" s="21">
         <v>32000</v>
-      </c>
-      <c r="DQ3" s="21">
-        <v>16000</v>
       </c>
       <c r="DR3" s="21">
         <v>32000</v>
@@ -2389,49 +2640,62 @@
         <v>1</v>
       </c>
       <c r="DU3" s="21">
-        <v>60000</v>
+        <v>32000</v>
       </c>
       <c r="DV3" s="21">
-        <v>60000</v>
+        <v>16000</v>
       </c>
       <c r="DW3" s="21">
-        <v>80000</v>
+        <v>32000</v>
       </c>
       <c r="DX3" s="26"/>
       <c r="DY3" s="20">
         <v>1</v>
       </c>
       <c r="DZ3" s="21">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="EA3" s="21">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="EB3" s="21">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="EC3" s="26"/>
       <c r="ED3" s="20">
         <v>1</v>
       </c>
-      <c r="EE3" s="21"/>
-      <c r="EF3" s="21"/>
-      <c r="EG3" s="21"/>
+      <c r="EE3" s="21">
+        <v>30000</v>
+      </c>
+      <c r="EF3" s="21">
+        <v>30000</v>
+      </c>
+      <c r="EG3" s="21">
+        <v>90000</v>
+      </c>
       <c r="EH3" s="26"/>
       <c r="EI3" s="20">
         <v>1</v>
       </c>
-      <c r="EJ3" s="21">
+      <c r="EJ3" s="21"/>
+      <c r="EK3" s="21"/>
+      <c r="EL3" s="21"/>
+      <c r="EM3" s="26"/>
+      <c r="EN3" s="20">
+        <v>1</v>
+      </c>
+      <c r="EO3" s="21">
         <v>6000</v>
       </c>
-      <c r="EK3" s="21">
+      <c r="EP3" s="21">
         <v>6000</v>
       </c>
-      <c r="EL3" s="21">
+      <c r="EQ3" s="21">
         <v>8000</v>
       </c>
     </row>
-    <row r="4" spans="2:142" ht="15.75" customHeight="1">
+    <row r="4" spans="2:147" ht="15.75" customHeight="1">
       <c r="B4" s="20">
         <v>2</v>
       </c>
@@ -2568,52 +2832,52 @@
         <v>2</v>
       </c>
       <c r="BC4" s="21">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="BD4" s="21">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="BE4" s="21">
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="BF4" s="26"/>
       <c r="BG4" s="20">
         <v>2</v>
       </c>
       <c r="BH4" s="21">
-        <v>7500</v>
+        <v>100000</v>
       </c>
       <c r="BI4" s="21">
-        <v>7500</v>
+        <v>100000</v>
       </c>
       <c r="BJ4" s="21">
-        <v>7500</v>
+        <v>300000</v>
       </c>
       <c r="BK4" s="26"/>
       <c r="BL4" s="20">
         <v>2</v>
       </c>
       <c r="BM4" s="21">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="BN4" s="21">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="BO4" s="21">
-        <v>16000</v>
+        <v>7500</v>
       </c>
       <c r="BP4" s="26"/>
       <c r="BQ4" s="20">
         <v>2</v>
       </c>
       <c r="BR4" s="21">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="BS4" s="21">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="BT4" s="21">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="BU4" s="26"/>
       <c r="BV4" s="20">
@@ -2633,10 +2897,10 @@
         <v>2</v>
       </c>
       <c r="CB4" s="21">
+        <v>2000</v>
+      </c>
+      <c r="CC4" s="21">
         <v>4000</v>
-      </c>
-      <c r="CC4" s="21">
-        <v>2000</v>
       </c>
       <c r="CD4" s="21">
         <v>4000</v>
@@ -2659,23 +2923,23 @@
         <v>2</v>
       </c>
       <c r="CL4" s="21">
-        <v>60000</v>
+        <v>4000</v>
       </c>
       <c r="CM4" s="21">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="CN4" s="21">
-        <v>60000</v>
+        <v>4000</v>
       </c>
       <c r="CO4" s="26"/>
       <c r="CP4" s="20">
         <v>2</v>
       </c>
       <c r="CQ4" s="21">
+        <v>60000</v>
+      </c>
+      <c r="CR4" s="21">
         <v>30000</v>
-      </c>
-      <c r="CR4" s="21">
-        <v>60000</v>
       </c>
       <c r="CS4" s="21">
         <v>60000</v>
@@ -2685,10 +2949,10 @@
         <v>2</v>
       </c>
       <c r="CV4" s="21">
+        <v>30000</v>
+      </c>
+      <c r="CW4" s="21">
         <v>60000</v>
-      </c>
-      <c r="CW4" s="21">
-        <v>30000</v>
       </c>
       <c r="CX4" s="21">
         <v>60000</v>
@@ -2698,10 +2962,10 @@
         <v>2</v>
       </c>
       <c r="DA4" s="21">
+        <v>60000</v>
+      </c>
+      <c r="DB4" s="21">
         <v>30000</v>
-      </c>
-      <c r="DB4" s="21">
-        <v>60000</v>
       </c>
       <c r="DC4" s="21">
         <v>60000</v>
@@ -2711,10 +2975,10 @@
         <v>2</v>
       </c>
       <c r="DF4" s="21">
+        <v>30000</v>
+      </c>
+      <c r="DG4" s="21">
         <v>60000</v>
-      </c>
-      <c r="DG4" s="21">
-        <v>30000</v>
       </c>
       <c r="DH4" s="21">
         <v>60000</v>
@@ -2724,23 +2988,23 @@
         <v>2</v>
       </c>
       <c r="DK4" s="21">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="DL4" s="21">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="DM4" s="21">
-        <v>80000</v>
+        <v>60000</v>
       </c>
       <c r="DN4" s="26"/>
       <c r="DO4" s="20">
         <v>2</v>
       </c>
       <c r="DP4" s="21">
+        <v>40000</v>
+      </c>
+      <c r="DQ4" s="21">
         <v>80000</v>
-      </c>
-      <c r="DQ4" s="21">
-        <v>40000</v>
       </c>
       <c r="DR4" s="21">
         <v>80000</v>
@@ -2750,49 +3014,62 @@
         <v>2</v>
       </c>
       <c r="DU4" s="21">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="DV4" s="21">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="DW4" s="21">
-        <v>160000</v>
+        <v>80000</v>
       </c>
       <c r="DX4" s="26"/>
       <c r="DY4" s="20">
         <v>2</v>
       </c>
       <c r="DZ4" s="21">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="EA4" s="21">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="EB4" s="21">
-        <v>180000</v>
+        <v>160000</v>
       </c>
       <c r="EC4" s="26"/>
       <c r="ED4" s="20">
         <v>2</v>
       </c>
-      <c r="EE4" s="21"/>
-      <c r="EF4" s="21"/>
-      <c r="EG4" s="21"/>
+      <c r="EE4" s="21">
+        <v>60000</v>
+      </c>
+      <c r="EF4" s="21">
+        <v>60000</v>
+      </c>
+      <c r="EG4" s="21">
+        <v>180000</v>
+      </c>
       <c r="EH4" s="26"/>
       <c r="EI4" s="20">
         <v>2</v>
       </c>
-      <c r="EJ4" s="21">
+      <c r="EJ4" s="21"/>
+      <c r="EK4" s="21"/>
+      <c r="EL4" s="21"/>
+      <c r="EM4" s="26"/>
+      <c r="EN4" s="20">
+        <v>2</v>
+      </c>
+      <c r="EO4" s="21">
         <v>24000</v>
       </c>
-      <c r="EK4" s="21">
+      <c r="EP4" s="21">
         <v>24000</v>
       </c>
-      <c r="EL4" s="21">
+      <c r="EQ4" s="21">
         <v>32000</v>
       </c>
     </row>
-    <row r="5" spans="2:142" ht="15.75" customHeight="1">
+    <row r="5" spans="2:147" ht="15.75" customHeight="1">
       <c r="B5" s="20">
         <v>3</v>
       </c>
@@ -2929,52 +3206,52 @@
         <v>3</v>
       </c>
       <c r="BC5" s="21">
-        <v>300000</v>
+        <v>15000</v>
       </c>
       <c r="BD5" s="21">
-        <v>300000</v>
+        <v>15000</v>
       </c>
       <c r="BE5" s="21">
-        <v>900000</v>
+        <v>30000</v>
       </c>
       <c r="BF5" s="26"/>
       <c r="BG5" s="20">
         <v>3</v>
       </c>
       <c r="BH5" s="21">
-        <v>15000</v>
+        <v>300000</v>
       </c>
       <c r="BI5" s="21">
-        <v>15000</v>
+        <v>300000</v>
       </c>
       <c r="BJ5" s="21">
-        <v>15000</v>
+        <v>900000</v>
       </c>
       <c r="BK5" s="26"/>
       <c r="BL5" s="20">
         <v>3</v>
       </c>
       <c r="BM5" s="21">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="BN5" s="21">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="BO5" s="21">
-        <v>24000</v>
+        <v>15000</v>
       </c>
       <c r="BP5" s="26"/>
       <c r="BQ5" s="20">
         <v>3</v>
       </c>
       <c r="BR5" s="21">
-        <v>2400</v>
+        <v>18000</v>
       </c>
       <c r="BS5" s="21">
-        <v>4800</v>
+        <v>18000</v>
       </c>
       <c r="BT5" s="21">
-        <v>4800</v>
+        <v>24000</v>
       </c>
       <c r="BU5" s="26"/>
       <c r="BV5" s="20">
@@ -2994,10 +3271,10 @@
         <v>3</v>
       </c>
       <c r="CB5" s="21">
+        <v>2400</v>
+      </c>
+      <c r="CC5" s="21">
         <v>4800</v>
-      </c>
-      <c r="CC5" s="21">
-        <v>2400</v>
       </c>
       <c r="CD5" s="21">
         <v>4800</v>
@@ -3020,23 +3297,23 @@
         <v>3</v>
       </c>
       <c r="CL5" s="21">
-        <v>88000</v>
+        <v>4800</v>
       </c>
       <c r="CM5" s="21">
-        <v>44000</v>
+        <v>2400</v>
       </c>
       <c r="CN5" s="21">
-        <v>88000</v>
+        <v>4800</v>
       </c>
       <c r="CO5" s="26"/>
       <c r="CP5" s="20">
         <v>3</v>
       </c>
       <c r="CQ5" s="21">
+        <v>88000</v>
+      </c>
+      <c r="CR5" s="21">
         <v>44000</v>
-      </c>
-      <c r="CR5" s="21">
-        <v>88000</v>
       </c>
       <c r="CS5" s="21">
         <v>88000</v>
@@ -3046,10 +3323,10 @@
         <v>3</v>
       </c>
       <c r="CV5" s="21">
+        <v>44000</v>
+      </c>
+      <c r="CW5" s="21">
         <v>88000</v>
-      </c>
-      <c r="CW5" s="21">
-        <v>44000</v>
       </c>
       <c r="CX5" s="21">
         <v>88000</v>
@@ -3059,10 +3336,10 @@
         <v>3</v>
       </c>
       <c r="DA5" s="21">
+        <v>88000</v>
+      </c>
+      <c r="DB5" s="21">
         <v>44000</v>
-      </c>
-      <c r="DB5" s="21">
-        <v>88000</v>
       </c>
       <c r="DC5" s="21">
         <v>88000</v>
@@ -3072,10 +3349,10 @@
         <v>3</v>
       </c>
       <c r="DF5" s="21">
+        <v>44000</v>
+      </c>
+      <c r="DG5" s="21">
         <v>88000</v>
-      </c>
-      <c r="DG5" s="21">
-        <v>44000</v>
       </c>
       <c r="DH5" s="21">
         <v>88000</v>
@@ -3085,23 +3362,23 @@
         <v>3</v>
       </c>
       <c r="DK5" s="21">
-        <v>72000</v>
+        <v>88000</v>
       </c>
       <c r="DL5" s="21">
-        <v>144000</v>
+        <v>44000</v>
       </c>
       <c r="DM5" s="21">
-        <v>144000</v>
+        <v>88000</v>
       </c>
       <c r="DN5" s="26"/>
       <c r="DO5" s="20">
         <v>3</v>
       </c>
       <c r="DP5" s="21">
+        <v>72000</v>
+      </c>
+      <c r="DQ5" s="21">
         <v>144000</v>
-      </c>
-      <c r="DQ5" s="21">
-        <v>72000</v>
       </c>
       <c r="DR5" s="21">
         <v>144000</v>
@@ -3111,55 +3388,68 @@
         <v>3</v>
       </c>
       <c r="DU5" s="21">
-        <v>240000</v>
+        <v>144000</v>
       </c>
       <c r="DV5" s="21">
-        <v>240000</v>
+        <v>72000</v>
       </c>
       <c r="DW5" s="21">
-        <v>320000</v>
+        <v>144000</v>
       </c>
       <c r="DX5" s="26"/>
       <c r="DY5" s="20">
         <v>3</v>
       </c>
       <c r="DZ5" s="21">
-        <v>120000</v>
+        <v>240000</v>
       </c>
       <c r="EA5" s="21">
-        <v>120000</v>
+        <v>240000</v>
       </c>
       <c r="EB5" s="21">
-        <v>360000</v>
+        <v>320000</v>
       </c>
       <c r="EC5" s="26"/>
       <c r="ED5" s="20">
         <v>3</v>
       </c>
       <c r="EE5" s="21">
-        <v>720</v>
+        <v>120000</v>
       </c>
       <c r="EF5" s="21">
-        <v>720</v>
+        <v>120000</v>
       </c>
       <c r="EG5" s="21">
-        <v>960</v>
+        <v>360000</v>
       </c>
       <c r="EH5" s="26"/>
       <c r="EI5" s="20">
         <v>3</v>
       </c>
       <c r="EJ5" s="21">
+        <v>720</v>
+      </c>
+      <c r="EK5" s="21">
+        <v>720</v>
+      </c>
+      <c r="EL5" s="21">
+        <v>960</v>
+      </c>
+      <c r="EM5" s="26"/>
+      <c r="EN5" s="20">
+        <v>3</v>
+      </c>
+      <c r="EO5" s="21">
         <v>54000</v>
       </c>
-      <c r="EK5" s="21">
+      <c r="EP5" s="21">
         <v>54000</v>
       </c>
-      <c r="EL5" s="21">
+      <c r="EQ5" s="21">
         <v>72000</v>
       </c>
     </row>
-    <row r="6" spans="2:142" ht="15.75" customHeight="1">
+    <row r="6" spans="2:147" ht="15.75" customHeight="1">
       <c r="B6" s="20">
         <v>4</v>
       </c>
@@ -3284,44 +3574,44 @@
         <v>278</v>
       </c>
       <c r="BA6" s="26"/>
+      <c r="BB6" s="20">
+        <v>4</v>
+      </c>
+      <c r="BC6" s="21">
+        <v>20000</v>
+      </c>
+      <c r="BD6" s="21">
+        <v>20000</v>
+      </c>
+      <c r="BE6" s="21">
+        <v>40000</v>
+      </c>
       <c r="BF6" s="26"/>
-      <c r="BG6" s="20">
-        <v>4</v>
-      </c>
-      <c r="BH6" s="21">
-        <v>30000</v>
-      </c>
-      <c r="BI6" s="21">
-        <v>30000</v>
-      </c>
-      <c r="BJ6" s="21">
-        <v>30000</v>
-      </c>
       <c r="BK6" s="26"/>
       <c r="BL6" s="20">
         <v>4</v>
       </c>
       <c r="BM6" s="21">
-        <v>24000</v>
+        <v>30000</v>
       </c>
       <c r="BN6" s="21">
-        <v>24000</v>
+        <v>30000</v>
       </c>
       <c r="BO6" s="21">
-        <v>32000</v>
+        <v>30000</v>
       </c>
       <c r="BP6" s="26"/>
       <c r="BQ6" s="20">
         <v>4</v>
       </c>
       <c r="BR6" s="21">
-        <v>2800</v>
+        <v>24000</v>
       </c>
       <c r="BS6" s="21">
-        <v>5600</v>
+        <v>24000</v>
       </c>
       <c r="BT6" s="21">
-        <v>5600</v>
+        <v>32000</v>
       </c>
       <c r="BU6" s="26"/>
       <c r="BV6" s="20">
@@ -3341,10 +3631,10 @@
         <v>4</v>
       </c>
       <c r="CB6" s="21">
+        <v>2800</v>
+      </c>
+      <c r="CC6" s="21">
         <v>5600</v>
-      </c>
-      <c r="CC6" s="21">
-        <v>2800</v>
       </c>
       <c r="CD6" s="21">
         <v>5600</v>
@@ -3367,23 +3657,23 @@
         <v>4</v>
       </c>
       <c r="CL6" s="21">
-        <v>112000</v>
+        <v>5600</v>
       </c>
       <c r="CM6" s="21">
-        <v>56000</v>
+        <v>2800</v>
       </c>
       <c r="CN6" s="21">
-        <v>112000</v>
+        <v>5600</v>
       </c>
       <c r="CO6" s="26"/>
       <c r="CP6" s="20">
         <v>4</v>
       </c>
       <c r="CQ6" s="21">
+        <v>112000</v>
+      </c>
+      <c r="CR6" s="21">
         <v>56000</v>
-      </c>
-      <c r="CR6" s="21">
-        <v>112000</v>
       </c>
       <c r="CS6" s="21">
         <v>112000</v>
@@ -3393,10 +3683,10 @@
         <v>4</v>
       </c>
       <c r="CV6" s="21">
+        <v>56000</v>
+      </c>
+      <c r="CW6" s="21">
         <v>112000</v>
-      </c>
-      <c r="CW6" s="21">
-        <v>56000</v>
       </c>
       <c r="CX6" s="21">
         <v>112000</v>
@@ -3406,10 +3696,10 @@
         <v>4</v>
       </c>
       <c r="DA6" s="21">
+        <v>112000</v>
+      </c>
+      <c r="DB6" s="21">
         <v>56000</v>
-      </c>
-      <c r="DB6" s="21">
-        <v>112000</v>
       </c>
       <c r="DC6" s="21">
         <v>112000</v>
@@ -3419,10 +3709,10 @@
         <v>4</v>
       </c>
       <c r="DF6" s="21">
+        <v>56000</v>
+      </c>
+      <c r="DG6" s="21">
         <v>112000</v>
-      </c>
-      <c r="DG6" s="21">
-        <v>56000</v>
       </c>
       <c r="DH6" s="21">
         <v>112000</v>
@@ -3432,23 +3722,23 @@
         <v>4</v>
       </c>
       <c r="DK6" s="21">
-        <v>144000</v>
+        <v>112000</v>
       </c>
       <c r="DL6" s="21">
-        <v>288000</v>
+        <v>56000</v>
       </c>
       <c r="DM6" s="21">
-        <v>288000</v>
+        <v>112000</v>
       </c>
       <c r="DN6" s="26"/>
       <c r="DO6" s="20">
         <v>4</v>
       </c>
       <c r="DP6" s="21">
+        <v>144000</v>
+      </c>
+      <c r="DQ6" s="21">
         <v>288000</v>
-      </c>
-      <c r="DQ6" s="21">
-        <v>144000</v>
       </c>
       <c r="DR6" s="21">
         <v>288000</v>
@@ -3458,55 +3748,68 @@
         <v>4</v>
       </c>
       <c r="DU6" s="21">
-        <v>480000</v>
+        <v>288000</v>
       </c>
       <c r="DV6" s="21">
-        <v>480000</v>
+        <v>144000</v>
       </c>
       <c r="DW6" s="21">
-        <v>640000</v>
+        <v>288000</v>
       </c>
       <c r="DX6" s="26"/>
       <c r="DY6" s="20">
         <v>4</v>
       </c>
       <c r="DZ6" s="21">
-        <v>240000</v>
+        <v>480000</v>
       </c>
       <c r="EA6" s="21">
-        <v>240000</v>
+        <v>480000</v>
       </c>
       <c r="EB6" s="21">
-        <v>720000</v>
+        <v>640000</v>
       </c>
       <c r="EC6" s="26"/>
       <c r="ED6" s="20">
         <v>4</v>
       </c>
       <c r="EE6" s="21">
-        <v>24000</v>
+        <v>240000</v>
       </c>
       <c r="EF6" s="21">
-        <v>24000</v>
+        <v>240000</v>
       </c>
       <c r="EG6" s="21">
-        <v>32000</v>
+        <v>720000</v>
       </c>
       <c r="EH6" s="26"/>
       <c r="EI6" s="20">
         <v>4</v>
       </c>
       <c r="EJ6" s="21">
+        <v>24000</v>
+      </c>
+      <c r="EK6" s="21">
+        <v>24000</v>
+      </c>
+      <c r="EL6" s="21">
+        <v>32000</v>
+      </c>
+      <c r="EM6" s="26"/>
+      <c r="EN6" s="20">
+        <v>4</v>
+      </c>
+      <c r="EO6" s="21">
         <v>144000</v>
       </c>
-      <c r="EK6" s="21">
+      <c r="EP6" s="21">
         <v>144000</v>
       </c>
-      <c r="EL6" s="21">
+      <c r="EQ6" s="21">
         <v>192000</v>
       </c>
     </row>
-    <row r="7" spans="2:142" ht="15.75" customHeight="1">
+    <row r="7" spans="2:147" ht="15.75" customHeight="1">
       <c r="B7" s="20">
         <v>5</v>
       </c>
@@ -3631,44 +3934,44 @@
         <v>279</v>
       </c>
       <c r="BA7" s="26"/>
+      <c r="BB7" s="20">
+        <v>5</v>
+      </c>
+      <c r="BC7" s="21">
+        <v>30000</v>
+      </c>
+      <c r="BD7" s="21">
+        <v>30000</v>
+      </c>
+      <c r="BE7" s="21">
+        <v>60000</v>
+      </c>
       <c r="BF7" s="26"/>
-      <c r="BG7" s="20">
-        <v>5</v>
-      </c>
-      <c r="BH7" s="21">
-        <v>45000</v>
-      </c>
-      <c r="BI7" s="21">
-        <v>45000</v>
-      </c>
-      <c r="BJ7" s="21">
-        <v>45000</v>
-      </c>
       <c r="BK7" s="26"/>
       <c r="BL7" s="20">
         <v>5</v>
       </c>
       <c r="BM7" s="21">
-        <v>36000</v>
+        <v>45000</v>
       </c>
       <c r="BN7" s="21">
-        <v>36000</v>
+        <v>45000</v>
       </c>
       <c r="BO7" s="21">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="BP7" s="26"/>
       <c r="BQ7" s="20">
         <v>5</v>
       </c>
       <c r="BR7" s="21">
-        <v>4800</v>
+        <v>36000</v>
       </c>
       <c r="BS7" s="21">
-        <v>9600</v>
+        <v>36000</v>
       </c>
       <c r="BT7" s="21">
-        <v>9600</v>
+        <v>48000</v>
       </c>
       <c r="BU7" s="26"/>
       <c r="BV7" s="20">
@@ -3688,10 +3991,10 @@
         <v>5</v>
       </c>
       <c r="CB7" s="21">
+        <v>4800</v>
+      </c>
+      <c r="CC7" s="21">
         <v>9600</v>
-      </c>
-      <c r="CC7" s="21">
-        <v>4800</v>
       </c>
       <c r="CD7" s="21">
         <v>9600</v>
@@ -3714,23 +4017,23 @@
         <v>5</v>
       </c>
       <c r="CL7" s="21">
-        <v>140000</v>
+        <v>9600</v>
       </c>
       <c r="CM7" s="21">
-        <v>70000</v>
+        <v>4800</v>
       </c>
       <c r="CN7" s="21">
-        <v>140000</v>
+        <v>9600</v>
       </c>
       <c r="CO7" s="26"/>
       <c r="CP7" s="20">
         <v>5</v>
       </c>
       <c r="CQ7" s="21">
+        <v>140000</v>
+      </c>
+      <c r="CR7" s="21">
         <v>70000</v>
-      </c>
-      <c r="CR7" s="21">
-        <v>140000</v>
       </c>
       <c r="CS7" s="21">
         <v>140000</v>
@@ -3740,10 +4043,10 @@
         <v>5</v>
       </c>
       <c r="CV7" s="21">
+        <v>70000</v>
+      </c>
+      <c r="CW7" s="21">
         <v>140000</v>
-      </c>
-      <c r="CW7" s="21">
-        <v>70000</v>
       </c>
       <c r="CX7" s="21">
         <v>140000</v>
@@ -3753,10 +4056,10 @@
         <v>5</v>
       </c>
       <c r="DA7" s="21">
+        <v>140000</v>
+      </c>
+      <c r="DB7" s="21">
         <v>70000</v>
-      </c>
-      <c r="DB7" s="21">
-        <v>140000</v>
       </c>
       <c r="DC7" s="21">
         <v>140000</v>
@@ -3766,10 +4069,10 @@
         <v>5</v>
       </c>
       <c r="DF7" s="21">
+        <v>70000</v>
+      </c>
+      <c r="DG7" s="21">
         <v>140000</v>
-      </c>
-      <c r="DG7" s="21">
-        <v>70000</v>
       </c>
       <c r="DH7" s="21">
         <v>140000</v>
@@ -3779,23 +4082,23 @@
         <v>5</v>
       </c>
       <c r="DK7" s="21">
-        <v>240000</v>
+        <v>140000</v>
       </c>
       <c r="DL7" s="21">
-        <v>480000</v>
+        <v>70000</v>
       </c>
       <c r="DM7" s="21">
-        <v>480000</v>
+        <v>140000</v>
       </c>
       <c r="DN7" s="26"/>
       <c r="DO7" s="20">
         <v>5</v>
       </c>
       <c r="DP7" s="21">
+        <v>240000</v>
+      </c>
+      <c r="DQ7" s="21">
         <v>480000</v>
-      </c>
-      <c r="DQ7" s="21">
-        <v>240000</v>
       </c>
       <c r="DR7" s="21">
         <v>480000</v>
@@ -3805,55 +4108,68 @@
         <v>5</v>
       </c>
       <c r="DU7" s="21">
-        <v>960000</v>
+        <v>480000</v>
       </c>
       <c r="DV7" s="21">
-        <v>960000</v>
+        <v>240000</v>
       </c>
       <c r="DW7" s="21">
-        <v>1280000</v>
+        <v>480000</v>
       </c>
       <c r="DX7" s="26"/>
       <c r="DY7" s="20">
         <v>5</v>
       </c>
       <c r="DZ7" s="21">
-        <v>480000</v>
+        <v>960000</v>
       </c>
       <c r="EA7" s="21">
-        <v>480000</v>
+        <v>960000</v>
       </c>
       <c r="EB7" s="21">
-        <v>1440000</v>
+        <v>1280000</v>
       </c>
       <c r="EC7" s="26"/>
       <c r="ED7" s="20">
         <v>5</v>
       </c>
       <c r="EE7" s="21">
-        <v>54000</v>
+        <v>480000</v>
       </c>
       <c r="EF7" s="21">
-        <v>54000</v>
+        <v>480000</v>
       </c>
       <c r="EG7" s="21">
-        <v>72000</v>
+        <v>1440000</v>
       </c>
       <c r="EH7" s="26"/>
       <c r="EI7" s="20">
         <v>5</v>
       </c>
       <c r="EJ7" s="21">
+        <v>54000</v>
+      </c>
+      <c r="EK7" s="21">
+        <v>54000</v>
+      </c>
+      <c r="EL7" s="21">
+        <v>72000</v>
+      </c>
+      <c r="EM7" s="26"/>
+      <c r="EN7" s="20">
+        <v>5</v>
+      </c>
+      <c r="EO7" s="21">
         <v>216000</v>
       </c>
-      <c r="EK7" s="21">
+      <c r="EP7" s="21">
         <v>216000</v>
       </c>
-      <c r="EL7" s="21">
+      <c r="EQ7" s="21">
         <v>288000</v>
       </c>
     </row>
-    <row r="8" spans="2:142" ht="15.75" customHeight="1">
+    <row r="8" spans="2:147" ht="15.75" customHeight="1">
       <c r="B8" s="20">
         <v>6</v>
       </c>
@@ -3971,26 +4287,14 @@
       <c r="AZ8" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="BG8" s="20">
-        <v>6</v>
-      </c>
-      <c r="BH8" s="21">
-        <v>80000</v>
-      </c>
-      <c r="BI8" s="21">
-        <v>80000</v>
-      </c>
-      <c r="BJ8" s="21">
-        <v>80000</v>
-      </c>
       <c r="BL8" s="20">
         <v>6</v>
       </c>
       <c r="BM8" s="21">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="BN8" s="21">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="BO8" s="21">
         <v>80000</v>
@@ -3999,13 +4303,13 @@
         <v>6</v>
       </c>
       <c r="BR8" s="21">
-        <v>9600</v>
+        <v>60000</v>
       </c>
       <c r="BS8" s="21">
-        <v>19200</v>
+        <v>60000</v>
       </c>
       <c r="BT8" s="21">
-        <v>19200</v>
+        <v>80000</v>
       </c>
       <c r="BV8" s="20">
         <v>6</v>
@@ -4023,10 +4327,10 @@
         <v>6</v>
       </c>
       <c r="CB8" s="21">
+        <v>9600</v>
+      </c>
+      <c r="CC8" s="21">
         <v>19200</v>
-      </c>
-      <c r="CC8" s="21">
-        <v>9600</v>
       </c>
       <c r="CD8" s="21">
         <v>19200</v>
@@ -4047,22 +4351,22 @@
         <v>6</v>
       </c>
       <c r="CL8" s="21">
-        <v>192000</v>
+        <v>19200</v>
       </c>
       <c r="CM8" s="21">
-        <v>96000</v>
+        <v>9600</v>
       </c>
       <c r="CN8" s="21">
-        <v>192000</v>
+        <v>19200</v>
       </c>
       <c r="CP8" s="20">
         <v>6</v>
       </c>
       <c r="CQ8" s="21">
+        <v>192000</v>
+      </c>
+      <c r="CR8" s="21">
         <v>96000</v>
-      </c>
-      <c r="CR8" s="21">
-        <v>192000</v>
       </c>
       <c r="CS8" s="21">
         <v>192000</v>
@@ -4071,10 +4375,10 @@
         <v>6</v>
       </c>
       <c r="CV8" s="21">
+        <v>96000</v>
+      </c>
+      <c r="CW8" s="21">
         <v>192000</v>
-      </c>
-      <c r="CW8" s="21">
-        <v>96000</v>
       </c>
       <c r="CX8" s="21">
         <v>192000</v>
@@ -4083,10 +4387,10 @@
         <v>6</v>
       </c>
       <c r="DA8" s="21">
+        <v>192000</v>
+      </c>
+      <c r="DB8" s="21">
         <v>96000</v>
-      </c>
-      <c r="DB8" s="21">
-        <v>192000</v>
       </c>
       <c r="DC8" s="21">
         <v>192000</v>
@@ -4095,20 +4399,32 @@
         <v>6</v>
       </c>
       <c r="DF8" s="21">
+        <v>96000</v>
+      </c>
+      <c r="DG8" s="21">
         <v>192000</v>
-      </c>
-      <c r="DG8" s="21">
-        <v>96000</v>
       </c>
       <c r="DH8" s="21">
         <v>192000</v>
       </c>
-      <c r="ED8" s="22"/>
-      <c r="EE8" s="23"/>
-      <c r="EF8" s="23"/>
-      <c r="EG8" s="23"/>
-    </row>
-    <row r="9" spans="2:142" ht="15.75" customHeight="1">
+      <c r="DJ8" s="20">
+        <v>6</v>
+      </c>
+      <c r="DK8" s="21">
+        <v>192000</v>
+      </c>
+      <c r="DL8" s="21">
+        <v>96000</v>
+      </c>
+      <c r="DM8" s="21">
+        <v>192000</v>
+      </c>
+      <c r="EI8" s="22"/>
+      <c r="EJ8" s="23"/>
+      <c r="EK8" s="23"/>
+      <c r="EL8" s="23"/>
+    </row>
+    <row r="9" spans="2:147" ht="15.75" customHeight="1">
       <c r="B9" s="20">
         <v>7</v>
       </c>
@@ -4226,26 +4542,14 @@
       <c r="AZ9" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="BG9" s="20">
-        <v>7</v>
-      </c>
-      <c r="BH9" s="21">
-        <v>120000</v>
-      </c>
-      <c r="BI9" s="21">
-        <v>120000</v>
-      </c>
-      <c r="BJ9" s="21">
-        <v>120000</v>
-      </c>
       <c r="BL9" s="20">
         <v>7</v>
       </c>
       <c r="BM9" s="21">
-        <v>90000</v>
+        <v>120000</v>
       </c>
       <c r="BN9" s="21">
-        <v>90000</v>
+        <v>120000</v>
       </c>
       <c r="BO9" s="21">
         <v>120000</v>
@@ -4254,13 +4558,13 @@
         <v>7</v>
       </c>
       <c r="BR9" s="21">
-        <v>14400</v>
+        <v>90000</v>
       </c>
       <c r="BS9" s="21">
-        <v>28800</v>
+        <v>90000</v>
       </c>
       <c r="BT9" s="21">
-        <v>28800</v>
+        <v>120000</v>
       </c>
       <c r="BV9" s="20">
         <v>7</v>
@@ -4278,10 +4582,10 @@
         <v>7</v>
       </c>
       <c r="CB9" s="21">
+        <v>14400</v>
+      </c>
+      <c r="CC9" s="21">
         <v>28800</v>
-      </c>
-      <c r="CC9" s="21">
-        <v>14400</v>
       </c>
       <c r="CD9" s="21">
         <v>28800</v>
@@ -4302,22 +4606,22 @@
         <v>7</v>
       </c>
       <c r="CL9" s="21">
-        <v>368000</v>
+        <v>28800</v>
       </c>
       <c r="CM9" s="21">
-        <v>184000</v>
+        <v>14400</v>
       </c>
       <c r="CN9" s="21">
-        <v>368000</v>
+        <v>28800</v>
       </c>
       <c r="CP9" s="20">
         <v>7</v>
       </c>
       <c r="CQ9" s="21">
+        <v>368000</v>
+      </c>
+      <c r="CR9" s="21">
         <v>184000</v>
-      </c>
-      <c r="CR9" s="21">
-        <v>368000</v>
       </c>
       <c r="CS9" s="21">
         <v>368000</v>
@@ -4326,10 +4630,10 @@
         <v>7</v>
       </c>
       <c r="CV9" s="21">
+        <v>184000</v>
+      </c>
+      <c r="CW9" s="21">
         <v>368000</v>
-      </c>
-      <c r="CW9" s="21">
-        <v>184000</v>
       </c>
       <c r="CX9" s="21">
         <v>368000</v>
@@ -4338,10 +4642,10 @@
         <v>7</v>
       </c>
       <c r="DA9" s="21">
+        <v>368000</v>
+      </c>
+      <c r="DB9" s="21">
         <v>184000</v>
-      </c>
-      <c r="DB9" s="21">
-        <v>368000</v>
       </c>
       <c r="DC9" s="21">
         <v>368000</v>
@@ -4350,20 +4654,32 @@
         <v>7</v>
       </c>
       <c r="DF9" s="21">
+        <v>184000</v>
+      </c>
+      <c r="DG9" s="21">
         <v>368000</v>
-      </c>
-      <c r="DG9" s="21">
-        <v>184000</v>
       </c>
       <c r="DH9" s="21">
         <v>368000</v>
       </c>
-      <c r="ED9" s="22"/>
-      <c r="EE9" s="23"/>
-      <c r="EF9" s="23"/>
-      <c r="EG9" s="23"/>
-    </row>
-    <row r="10" spans="2:142" ht="15.75" customHeight="1">
+      <c r="DJ9" s="20">
+        <v>7</v>
+      </c>
+      <c r="DK9" s="21">
+        <v>368000</v>
+      </c>
+      <c r="DL9" s="21">
+        <v>184000</v>
+      </c>
+      <c r="DM9" s="21">
+        <v>368000</v>
+      </c>
+      <c r="EI9" s="22"/>
+      <c r="EJ9" s="23"/>
+      <c r="EK9" s="23"/>
+      <c r="EL9" s="23"/>
+    </row>
+    <row r="10" spans="2:147" ht="15.75" customHeight="1">
       <c r="B10" s="20">
         <v>8</v>
       </c>
@@ -4389,7 +4705,9 @@
       <c r="J10" s="21">
         <v>16000</v>
       </c>
-      <c r="K10" s="20"/>
+      <c r="K10" s="20" t="s">
+        <v>296</v>
+      </c>
       <c r="L10" s="29"/>
       <c r="M10" s="20">
         <v>8</v>
@@ -4479,41 +4797,29 @@
       <c r="AZ10" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="BG10" s="20">
-        <v>8</v>
-      </c>
-      <c r="BH10" s="21">
-        <v>180000</v>
-      </c>
-      <c r="BI10" s="21">
-        <v>180000</v>
-      </c>
-      <c r="BJ10" s="21">
-        <v>180000</v>
-      </c>
       <c r="BL10" s="20">
         <v>8</v>
       </c>
       <c r="BM10" s="21">
-        <v>126000</v>
+        <v>180000</v>
       </c>
       <c r="BN10" s="21">
-        <v>126000</v>
+        <v>180000</v>
       </c>
       <c r="BO10" s="21">
-        <v>168000</v>
+        <v>180000</v>
       </c>
       <c r="BQ10" s="20">
         <v>8</v>
       </c>
       <c r="BR10" s="21">
-        <v>22000</v>
+        <v>126000</v>
       </c>
       <c r="BS10" s="21">
-        <v>44000</v>
+        <v>126000</v>
       </c>
       <c r="BT10" s="21">
-        <v>44000</v>
+        <v>168000</v>
       </c>
       <c r="BV10" s="20">
         <v>8</v>
@@ -4531,10 +4837,10 @@
         <v>8</v>
       </c>
       <c r="CB10" s="21">
+        <v>22000</v>
+      </c>
+      <c r="CC10" s="21">
         <v>44000</v>
-      </c>
-      <c r="CC10" s="21">
-        <v>22000</v>
       </c>
       <c r="CD10" s="21">
         <v>44000</v>
@@ -4555,22 +4861,22 @@
         <v>8</v>
       </c>
       <c r="CL10" s="21">
-        <v>520000</v>
+        <v>44000</v>
       </c>
       <c r="CM10" s="21">
-        <v>260000</v>
+        <v>22000</v>
       </c>
       <c r="CN10" s="21">
-        <v>520000</v>
+        <v>44000</v>
       </c>
       <c r="CP10" s="20">
         <v>8</v>
       </c>
       <c r="CQ10" s="21">
+        <v>520000</v>
+      </c>
+      <c r="CR10" s="21">
         <v>260000</v>
-      </c>
-      <c r="CR10" s="21">
-        <v>520000</v>
       </c>
       <c r="CS10" s="21">
         <v>520000</v>
@@ -4579,10 +4885,10 @@
         <v>8</v>
       </c>
       <c r="CV10" s="21">
+        <v>260000</v>
+      </c>
+      <c r="CW10" s="21">
         <v>520000</v>
-      </c>
-      <c r="CW10" s="21">
-        <v>260000</v>
       </c>
       <c r="CX10" s="21">
         <v>520000</v>
@@ -4591,10 +4897,10 @@
         <v>8</v>
       </c>
       <c r="DA10" s="21">
+        <v>520000</v>
+      </c>
+      <c r="DB10" s="21">
         <v>260000</v>
-      </c>
-      <c r="DB10" s="21">
-        <v>520000</v>
       </c>
       <c r="DC10" s="21">
         <v>520000</v>
@@ -4603,20 +4909,32 @@
         <v>8</v>
       </c>
       <c r="DF10" s="21">
+        <v>260000</v>
+      </c>
+      <c r="DG10" s="21">
         <v>520000</v>
-      </c>
-      <c r="DG10" s="21">
-        <v>260000</v>
       </c>
       <c r="DH10" s="21">
         <v>520000</v>
       </c>
-      <c r="ED10" s="22"/>
-      <c r="EE10" s="23"/>
-      <c r="EF10" s="23"/>
-      <c r="EG10" s="23"/>
-    </row>
-    <row r="11" spans="2:142" ht="15.75" customHeight="1">
+      <c r="DJ10" s="20">
+        <v>8</v>
+      </c>
+      <c r="DK10" s="21">
+        <v>520000</v>
+      </c>
+      <c r="DL10" s="21">
+        <v>260000</v>
+      </c>
+      <c r="DM10" s="21">
+        <v>520000</v>
+      </c>
+      <c r="EI10" s="22"/>
+      <c r="EJ10" s="23"/>
+      <c r="EK10" s="23"/>
+      <c r="EL10" s="23"/>
+    </row>
+    <row r="11" spans="2:147" ht="15.75" customHeight="1">
       <c r="B11" s="20">
         <v>9</v>
       </c>
@@ -4642,7 +4960,9 @@
       <c r="J11" s="21">
         <v>20000</v>
       </c>
-      <c r="K11" s="20"/>
+      <c r="K11" s="20" t="s">
+        <v>297</v>
+      </c>
       <c r="L11" s="29"/>
       <c r="M11" s="20">
         <v>9</v>
@@ -4656,7 +4976,7 @@
       <c r="P11" s="21">
         <v>6480</v>
       </c>
-      <c r="Q11" s="39" t="s">
+      <c r="Q11" s="34" t="s">
         <v>190</v>
       </c>
       <c r="S11" s="20">
@@ -4732,41 +5052,29 @@
       <c r="AZ11" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="BG11" s="20">
-        <v>9</v>
-      </c>
-      <c r="BH11" s="21">
-        <v>270000</v>
-      </c>
-      <c r="BI11" s="21">
-        <v>270000</v>
-      </c>
-      <c r="BJ11" s="21">
-        <v>270000</v>
-      </c>
       <c r="BL11" s="20">
         <v>9</v>
       </c>
       <c r="BM11" s="21">
-        <v>192000</v>
+        <v>270000</v>
       </c>
       <c r="BN11" s="21">
-        <v>192000</v>
+        <v>270000</v>
       </c>
       <c r="BO11" s="21">
-        <v>256000</v>
+        <v>270000</v>
       </c>
       <c r="BQ11" s="20">
         <v>9</v>
       </c>
       <c r="BR11" s="21">
-        <v>44000</v>
+        <v>192000</v>
       </c>
       <c r="BS11" s="21">
-        <v>88000</v>
+        <v>192000</v>
       </c>
       <c r="BT11" s="21">
-        <v>88000</v>
+        <v>256000</v>
       </c>
       <c r="BV11" s="20">
         <v>9</v>
@@ -4784,10 +5092,10 @@
         <v>9</v>
       </c>
       <c r="CB11" s="21">
+        <v>44000</v>
+      </c>
+      <c r="CC11" s="21">
         <v>88000</v>
-      </c>
-      <c r="CC11" s="21">
-        <v>44000</v>
       </c>
       <c r="CD11" s="21">
         <v>88000</v>
@@ -4808,22 +5116,22 @@
         <v>9</v>
       </c>
       <c r="CL11" s="21">
-        <v>840000</v>
+        <v>88000</v>
       </c>
       <c r="CM11" s="21">
-        <v>420000</v>
+        <v>44000</v>
       </c>
       <c r="CN11" s="21">
-        <v>840000</v>
+        <v>88000</v>
       </c>
       <c r="CP11" s="20">
         <v>9</v>
       </c>
       <c r="CQ11" s="21">
+        <v>840000</v>
+      </c>
+      <c r="CR11" s="21">
         <v>420000</v>
-      </c>
-      <c r="CR11" s="21">
-        <v>840000</v>
       </c>
       <c r="CS11" s="21">
         <v>840000</v>
@@ -4832,10 +5140,10 @@
         <v>9</v>
       </c>
       <c r="CV11" s="21">
+        <v>420000</v>
+      </c>
+      <c r="CW11" s="21">
         <v>840000</v>
-      </c>
-      <c r="CW11" s="21">
-        <v>420000</v>
       </c>
       <c r="CX11" s="21">
         <v>840000</v>
@@ -4844,10 +5152,10 @@
         <v>9</v>
       </c>
       <c r="DA11" s="21">
+        <v>840000</v>
+      </c>
+      <c r="DB11" s="21">
         <v>420000</v>
-      </c>
-      <c r="DB11" s="21">
-        <v>840000</v>
       </c>
       <c r="DC11" s="21">
         <v>840000</v>
@@ -4856,20 +5164,32 @@
         <v>9</v>
       </c>
       <c r="DF11" s="21">
+        <v>420000</v>
+      </c>
+      <c r="DG11" s="21">
         <v>840000</v>
-      </c>
-      <c r="DG11" s="21">
-        <v>420000</v>
       </c>
       <c r="DH11" s="21">
         <v>840000</v>
       </c>
-      <c r="ED11" s="22"/>
-      <c r="EE11" s="23"/>
-      <c r="EF11" s="23"/>
-      <c r="EG11" s="23"/>
-    </row>
-    <row r="12" spans="2:142" ht="15.75" customHeight="1">
+      <c r="DJ11" s="20">
+        <v>9</v>
+      </c>
+      <c r="DK11" s="21">
+        <v>840000</v>
+      </c>
+      <c r="DL11" s="21">
+        <v>420000</v>
+      </c>
+      <c r="DM11" s="21">
+        <v>840000</v>
+      </c>
+      <c r="EI11" s="22"/>
+      <c r="EJ11" s="23"/>
+      <c r="EK11" s="23"/>
+      <c r="EL11" s="23"/>
+    </row>
+    <row r="12" spans="2:147" ht="15.75" customHeight="1">
       <c r="B12" s="20">
         <v>10</v>
       </c>
@@ -4895,7 +5215,9 @@
       <c r="J12" s="21">
         <v>48000</v>
       </c>
-      <c r="K12" s="20"/>
+      <c r="K12" s="20" t="s">
+        <v>298</v>
+      </c>
       <c r="L12" s="29"/>
       <c r="M12" s="20">
         <v>10</v>
@@ -4909,7 +5231,7 @@
       <c r="P12" s="21">
         <v>7200</v>
       </c>
-      <c r="Q12" s="39" t="s">
+      <c r="Q12" s="34" t="s">
         <v>191</v>
       </c>
       <c r="S12" s="20">
@@ -4985,41 +5307,29 @@
       <c r="AZ12" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="BG12" s="20">
-        <v>10</v>
-      </c>
-      <c r="BH12" s="21">
-        <v>390000</v>
-      </c>
-      <c r="BI12" s="21">
-        <v>390000</v>
-      </c>
-      <c r="BJ12" s="21">
-        <v>390000</v>
-      </c>
       <c r="BL12" s="20">
         <v>10</v>
       </c>
       <c r="BM12" s="21">
-        <v>252000</v>
+        <v>390000</v>
       </c>
       <c r="BN12" s="21">
-        <v>252000</v>
+        <v>390000</v>
       </c>
       <c r="BO12" s="21">
-        <v>336000</v>
+        <v>390000</v>
       </c>
       <c r="BQ12" s="20">
         <v>10</v>
       </c>
       <c r="BR12" s="21">
-        <v>88000</v>
+        <v>252000</v>
       </c>
       <c r="BS12" s="21">
-        <v>176000</v>
+        <v>252000</v>
       </c>
       <c r="BT12" s="21">
-        <v>176000</v>
+        <v>336000</v>
       </c>
       <c r="BV12" s="20">
         <v>10</v>
@@ -5037,10 +5347,10 @@
         <v>10</v>
       </c>
       <c r="CB12" s="21">
+        <v>88000</v>
+      </c>
+      <c r="CC12" s="21">
         <v>176000</v>
-      </c>
-      <c r="CC12" s="21">
-        <v>88000</v>
       </c>
       <c r="CD12" s="21">
         <v>176000</v>
@@ -5061,22 +5371,22 @@
         <v>10</v>
       </c>
       <c r="CL12" s="21">
-        <v>1200000</v>
+        <v>176000</v>
       </c>
       <c r="CM12" s="21">
-        <v>600000</v>
+        <v>88000</v>
       </c>
       <c r="CN12" s="21">
-        <v>1200000</v>
+        <v>176000</v>
       </c>
       <c r="CP12" s="20">
         <v>10</v>
       </c>
       <c r="CQ12" s="21">
+        <v>1200000</v>
+      </c>
+      <c r="CR12" s="21">
         <v>600000</v>
-      </c>
-      <c r="CR12" s="21">
-        <v>1200000</v>
       </c>
       <c r="CS12" s="21">
         <v>1200000</v>
@@ -5085,10 +5395,10 @@
         <v>10</v>
       </c>
       <c r="CV12" s="21">
+        <v>600000</v>
+      </c>
+      <c r="CW12" s="21">
         <v>1200000</v>
-      </c>
-      <c r="CW12" s="21">
-        <v>600000</v>
       </c>
       <c r="CX12" s="21">
         <v>1200000</v>
@@ -5097,10 +5407,10 @@
         <v>10</v>
       </c>
       <c r="DA12" s="21">
+        <v>1200000</v>
+      </c>
+      <c r="DB12" s="21">
         <v>600000</v>
-      </c>
-      <c r="DB12" s="21">
-        <v>1200000</v>
       </c>
       <c r="DC12" s="21">
         <v>1200000</v>
@@ -5109,20 +5419,32 @@
         <v>10</v>
       </c>
       <c r="DF12" s="21">
+        <v>600000</v>
+      </c>
+      <c r="DG12" s="21">
         <v>1200000</v>
-      </c>
-      <c r="DG12" s="21">
-        <v>600000</v>
       </c>
       <c r="DH12" s="21">
         <v>1200000</v>
       </c>
-      <c r="ED12" s="22"/>
-      <c r="EE12" s="23"/>
-      <c r="EF12" s="23"/>
-      <c r="EG12" s="23"/>
-    </row>
-    <row r="13" spans="2:142" ht="15.75" customHeight="1">
+      <c r="DJ12" s="20">
+        <v>10</v>
+      </c>
+      <c r="DK12" s="21">
+        <v>1200000</v>
+      </c>
+      <c r="DL12" s="21">
+        <v>600000</v>
+      </c>
+      <c r="DM12" s="21">
+        <v>1200000</v>
+      </c>
+      <c r="EI12" s="22"/>
+      <c r="EJ12" s="23"/>
+      <c r="EK12" s="23"/>
+      <c r="EL12" s="23"/>
+    </row>
+    <row r="13" spans="2:147" ht="15.75" customHeight="1">
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
@@ -5154,7 +5476,7 @@
       <c r="P13" s="21">
         <v>19800</v>
       </c>
-      <c r="Q13" s="39" t="s">
+      <c r="Q13" s="34" t="s">
         <v>194</v>
       </c>
       <c r="S13" s="20">
@@ -5167,7 +5489,7 @@
         <v>19800</v>
       </c>
       <c r="V13" s="21"/>
-      <c r="W13" s="39" t="s">
+      <c r="W13" s="34" t="s">
         <v>128</v>
       </c>
       <c r="Y13" s="20">
@@ -5180,7 +5502,7 @@
       <c r="AB13" s="21">
         <v>19800</v>
       </c>
-      <c r="AC13" s="39" t="s">
+      <c r="AC13" s="34" t="s">
         <v>138</v>
       </c>
       <c r="AE13" s="20">
@@ -5193,7 +5515,7 @@
       <c r="AH13" s="21">
         <v>19800</v>
       </c>
-      <c r="AI13" s="39" t="s">
+      <c r="AI13" s="34" t="s">
         <v>148</v>
       </c>
       <c r="AK13" s="23"/>
@@ -5230,20 +5552,20 @@
       <c r="AZ13" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="BG13" s="23"/>
-      <c r="BH13" s="23"/>
-      <c r="BI13" s="23"/>
-      <c r="BJ13" s="23"/>
       <c r="BL13" s="23"/>
       <c r="BM13" s="23"/>
       <c r="BN13" s="23"/>
       <c r="BO13" s="23"/>
-      <c r="ED13" s="22"/>
-      <c r="EE13" s="23"/>
-      <c r="EF13" s="23"/>
-      <c r="EG13" s="23"/>
-    </row>
-    <row r="14" spans="2:142" ht="15.75" customHeight="1">
+      <c r="BQ13" s="23"/>
+      <c r="BR13" s="23"/>
+      <c r="BS13" s="23"/>
+      <c r="BT13" s="23"/>
+      <c r="EI13" s="22"/>
+      <c r="EJ13" s="23"/>
+      <c r="EK13" s="23"/>
+      <c r="EL13" s="23"/>
+    </row>
+    <row r="14" spans="2:147" ht="15.75" customHeight="1">
       <c r="F14" s="30"/>
       <c r="G14" s="20">
         <v>12</v>
@@ -5271,7 +5593,7 @@
       <c r="P14" s="21">
         <v>21600</v>
       </c>
-      <c r="Q14" s="38" t="s">
+      <c r="Q14" s="33" t="s">
         <v>195</v>
       </c>
       <c r="S14" s="20">
@@ -5284,7 +5606,7 @@
         <v>21600</v>
       </c>
       <c r="V14" s="21"/>
-      <c r="W14" s="38" t="s">
+      <c r="W14" s="33" t="s">
         <v>129</v>
       </c>
       <c r="Y14" s="20">
@@ -5297,7 +5619,7 @@
       <c r="AB14" s="21">
         <v>21600</v>
       </c>
-      <c r="AC14" s="38" t="s">
+      <c r="AC14" s="33" t="s">
         <v>139</v>
       </c>
       <c r="AE14" s="20">
@@ -5310,7 +5632,7 @@
       <c r="AH14" s="21">
         <v>21600</v>
       </c>
-      <c r="AI14" s="38" t="s">
+      <c r="AI14" s="33" t="s">
         <v>149</v>
       </c>
       <c r="AK14" s="23"/>
@@ -5347,16 +5669,16 @@
       <c r="AZ14" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="BG14" s="23"/>
-      <c r="BH14" s="23"/>
-      <c r="BI14" s="23"/>
-      <c r="BJ14" s="23"/>
-      <c r="ED14" s="22"/>
-      <c r="EE14" s="23"/>
-      <c r="EF14" s="23"/>
-      <c r="EG14" s="23"/>
-    </row>
-    <row r="15" spans="2:142" ht="15.75" customHeight="1">
+      <c r="BL14" s="23"/>
+      <c r="BM14" s="23"/>
+      <c r="BN14" s="23"/>
+      <c r="BO14" s="23"/>
+      <c r="EI14" s="22"/>
+      <c r="EJ14" s="23"/>
+      <c r="EK14" s="23"/>
+      <c r="EL14" s="23"/>
+    </row>
+    <row r="15" spans="2:147" ht="15.75" customHeight="1">
       <c r="F15" s="30"/>
       <c r="G15" s="20">
         <v>13</v>
@@ -5384,7 +5706,7 @@
       <c r="P15" s="21">
         <v>23400</v>
       </c>
-      <c r="Q15" s="38" t="s">
+      <c r="Q15" s="33" t="s">
         <v>192</v>
       </c>
       <c r="S15" s="20">
@@ -5397,7 +5719,7 @@
         <v>23400</v>
       </c>
       <c r="V15" s="21"/>
-      <c r="W15" s="38" t="s">
+      <c r="W15" s="33" t="s">
         <v>130</v>
       </c>
       <c r="Y15" s="20">
@@ -5410,7 +5732,7 @@
       <c r="AB15" s="21">
         <v>23400</v>
       </c>
-      <c r="AC15" s="38" t="s">
+      <c r="AC15" s="33" t="s">
         <v>140</v>
       </c>
       <c r="AE15" s="20">
@@ -5423,7 +5745,7 @@
       <c r="AH15" s="21">
         <v>23400</v>
       </c>
-      <c r="AI15" s="38" t="s">
+      <c r="AI15" s="33" t="s">
         <v>150</v>
       </c>
       <c r="AK15" s="23"/>
@@ -5460,16 +5782,16 @@
       <c r="AZ15" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="BG15" s="23"/>
-      <c r="BH15" s="23"/>
-      <c r="BI15" s="23"/>
-      <c r="BJ15" s="23"/>
-      <c r="ED15" s="22"/>
-      <c r="EE15" s="23"/>
-      <c r="EF15" s="23"/>
-      <c r="EG15" s="23"/>
-    </row>
-    <row r="16" spans="2:142" ht="15.75" customHeight="1">
+      <c r="BL15" s="23"/>
+      <c r="BM15" s="23"/>
+      <c r="BN15" s="23"/>
+      <c r="BO15" s="23"/>
+      <c r="EI15" s="22"/>
+      <c r="EJ15" s="23"/>
+      <c r="EK15" s="23"/>
+      <c r="EL15" s="23"/>
+    </row>
+    <row r="16" spans="2:147" ht="15.75" customHeight="1">
       <c r="F16" s="30"/>
       <c r="G16" s="20">
         <v>14</v>
@@ -5497,7 +5819,7 @@
       <c r="P16" s="21">
         <v>25200</v>
       </c>
-      <c r="Q16" s="38" t="s">
+      <c r="Q16" s="33" t="s">
         <v>193</v>
       </c>
       <c r="S16" s="20">
@@ -5510,7 +5832,7 @@
         <v>25200</v>
       </c>
       <c r="V16" s="21"/>
-      <c r="W16" s="38" t="s">
+      <c r="W16" s="33" t="s">
         <v>251</v>
       </c>
       <c r="Y16" s="20">
@@ -5523,7 +5845,7 @@
       <c r="AB16" s="21">
         <v>25200</v>
       </c>
-      <c r="AC16" s="38" t="s">
+      <c r="AC16" s="33" t="s">
         <v>257</v>
       </c>
       <c r="AE16" s="20">
@@ -5536,7 +5858,7 @@
       <c r="AH16" s="21">
         <v>25200</v>
       </c>
-      <c r="AI16" s="38" t="s">
+      <c r="AI16" s="33" t="s">
         <v>263</v>
       </c>
       <c r="AK16" s="23"/>
@@ -5573,16 +5895,16 @@
       <c r="AZ16" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="BG16" s="23"/>
-      <c r="BH16" s="23"/>
-      <c r="BI16" s="23"/>
-      <c r="BJ16" s="23"/>
-      <c r="ED16" s="22"/>
-      <c r="EE16" s="23"/>
-      <c r="EF16" s="23"/>
-      <c r="EG16" s="23"/>
-    </row>
-    <row r="17" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL16" s="23"/>
+      <c r="BM16" s="23"/>
+      <c r="BN16" s="23"/>
+      <c r="BO16" s="23"/>
+      <c r="EI16" s="22"/>
+      <c r="EJ16" s="23"/>
+      <c r="EK16" s="23"/>
+      <c r="EL16" s="23"/>
+    </row>
+    <row r="17" spans="2:142" ht="15.75" customHeight="1">
       <c r="F17" s="30"/>
       <c r="G17" s="20">
         <v>15</v>
@@ -5610,7 +5932,7 @@
       <c r="P17" s="21">
         <v>27000</v>
       </c>
-      <c r="Q17" s="38" t="s">
+      <c r="Q17" s="33" t="s">
         <v>196</v>
       </c>
       <c r="S17" s="20">
@@ -5623,7 +5945,7 @@
         <v>27000</v>
       </c>
       <c r="V17" s="21"/>
-      <c r="W17" s="38" t="s">
+      <c r="W17" s="33" t="s">
         <v>252</v>
       </c>
       <c r="Y17" s="20">
@@ -5636,7 +5958,7 @@
       <c r="AB17" s="21">
         <v>27000</v>
       </c>
-      <c r="AC17" s="38" t="s">
+      <c r="AC17" s="33" t="s">
         <v>258</v>
       </c>
       <c r="AE17" s="20">
@@ -5649,7 +5971,7 @@
       <c r="AH17" s="21">
         <v>27000</v>
       </c>
-      <c r="AI17" s="38" t="s">
+      <c r="AI17" s="33" t="s">
         <v>264</v>
       </c>
       <c r="AK17" s="23"/>
@@ -5686,16 +6008,16 @@
       <c r="AZ17" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="BG17" s="23"/>
-      <c r="BH17" s="23"/>
-      <c r="BI17" s="23"/>
-      <c r="BJ17" s="23"/>
-      <c r="ED17" s="22"/>
-      <c r="EE17" s="23"/>
-      <c r="EF17" s="23"/>
-      <c r="EG17" s="23"/>
-    </row>
-    <row r="18" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL17" s="23"/>
+      <c r="BM17" s="23"/>
+      <c r="BN17" s="23"/>
+      <c r="BO17" s="23"/>
+      <c r="EI17" s="22"/>
+      <c r="EJ17" s="23"/>
+      <c r="EK17" s="23"/>
+      <c r="EL17" s="23"/>
+    </row>
+    <row r="18" spans="2:142" ht="15.75" customHeight="1">
       <c r="F18" s="30"/>
       <c r="G18" s="20">
         <v>16</v>
@@ -5723,7 +6045,7 @@
       <c r="P18" s="21">
         <v>34560</v>
       </c>
-      <c r="Q18" s="38" t="s">
+      <c r="Q18" s="33" t="s">
         <v>197</v>
       </c>
       <c r="S18" s="20">
@@ -5736,7 +6058,7 @@
         <v>34560</v>
       </c>
       <c r="V18" s="21"/>
-      <c r="W18" s="38" t="s">
+      <c r="W18" s="33" t="s">
         <v>253</v>
       </c>
       <c r="Y18" s="20">
@@ -5749,7 +6071,7 @@
       <c r="AB18" s="21">
         <v>34560</v>
       </c>
-      <c r="AC18" s="38" t="s">
+      <c r="AC18" s="33" t="s">
         <v>259</v>
       </c>
       <c r="AE18" s="20">
@@ -5762,7 +6084,7 @@
       <c r="AH18" s="21">
         <v>34560</v>
       </c>
-      <c r="AI18" s="38" t="s">
+      <c r="AI18" s="33" t="s">
         <v>265</v>
       </c>
       <c r="AK18" s="23"/>
@@ -5799,16 +6121,16 @@
       <c r="AZ18" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="BG18" s="23"/>
-      <c r="BH18" s="23"/>
-      <c r="BI18" s="23"/>
-      <c r="BJ18" s="23"/>
-      <c r="ED18" s="22"/>
-      <c r="EE18" s="23"/>
-      <c r="EF18" s="23"/>
-      <c r="EG18" s="23"/>
-    </row>
-    <row r="19" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL18" s="23"/>
+      <c r="BM18" s="23"/>
+      <c r="BN18" s="23"/>
+      <c r="BO18" s="23"/>
+      <c r="EI18" s="22"/>
+      <c r="EJ18" s="23"/>
+      <c r="EK18" s="23"/>
+      <c r="EL18" s="23"/>
+    </row>
+    <row r="19" spans="2:142" ht="15.75" customHeight="1">
       <c r="F19" s="30"/>
       <c r="G19" s="20">
         <v>17</v>
@@ -5836,7 +6158,7 @@
       <c r="P19" s="21">
         <v>36720</v>
       </c>
-      <c r="Q19" s="38" t="s">
+      <c r="Q19" s="33" t="s">
         <v>198</v>
       </c>
       <c r="S19" s="20">
@@ -5849,7 +6171,7 @@
         <v>36720</v>
       </c>
       <c r="V19" s="21"/>
-      <c r="W19" s="38" t="s">
+      <c r="W19" s="33" t="s">
         <v>254</v>
       </c>
       <c r="Y19" s="20">
@@ -5862,7 +6184,7 @@
       <c r="AB19" s="21">
         <v>36720</v>
       </c>
-      <c r="AC19" s="38" t="s">
+      <c r="AC19" s="33" t="s">
         <v>260</v>
       </c>
       <c r="AE19" s="20">
@@ -5875,7 +6197,7 @@
       <c r="AH19" s="21">
         <v>36720</v>
       </c>
-      <c r="AI19" s="38" t="s">
+      <c r="AI19" s="33" t="s">
         <v>266</v>
       </c>
       <c r="AK19" s="23"/>
@@ -5912,16 +6234,16 @@
       <c r="AZ19" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="BG19" s="23"/>
-      <c r="BH19" s="23"/>
-      <c r="BI19" s="23"/>
-      <c r="BJ19" s="23"/>
-      <c r="ED19" s="22"/>
-      <c r="EE19" s="23"/>
-      <c r="EF19" s="23"/>
-      <c r="EG19" s="23"/>
-    </row>
-    <row r="20" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL19" s="23"/>
+      <c r="BM19" s="23"/>
+      <c r="BN19" s="23"/>
+      <c r="BO19" s="23"/>
+      <c r="EI19" s="22"/>
+      <c r="EJ19" s="23"/>
+      <c r="EK19" s="23"/>
+      <c r="EL19" s="23"/>
+    </row>
+    <row r="20" spans="2:142" ht="15.75" customHeight="1">
       <c r="F20" s="30"/>
       <c r="G20" s="20">
         <v>18</v>
@@ -5949,7 +6271,7 @@
       <c r="P20" s="21">
         <v>38880</v>
       </c>
-      <c r="Q20" s="38" t="s">
+      <c r="Q20" s="33" t="s">
         <v>199</v>
       </c>
       <c r="S20" s="20">
@@ -5962,7 +6284,7 @@
         <v>38880</v>
       </c>
       <c r="V20" s="21"/>
-      <c r="W20" s="38" t="s">
+      <c r="W20" s="33" t="s">
         <v>255</v>
       </c>
       <c r="Y20" s="20">
@@ -5975,7 +6297,7 @@
       <c r="AB20" s="21">
         <v>38880</v>
       </c>
-      <c r="AC20" s="38" t="s">
+      <c r="AC20" s="33" t="s">
         <v>261</v>
       </c>
       <c r="AE20" s="20">
@@ -5988,7 +6310,7 @@
       <c r="AH20" s="21">
         <v>38880</v>
       </c>
-      <c r="AI20" s="38" t="s">
+      <c r="AI20" s="33" t="s">
         <v>267</v>
       </c>
       <c r="AK20" s="23"/>
@@ -6025,16 +6347,16 @@
       <c r="AZ20" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="BG20" s="23"/>
-      <c r="BH20" s="23"/>
-      <c r="BI20" s="23"/>
-      <c r="BJ20" s="23"/>
-      <c r="ED20" s="22"/>
-      <c r="EE20" s="23"/>
-      <c r="EF20" s="23"/>
-      <c r="EG20" s="23"/>
-    </row>
-    <row r="21" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL20" s="23"/>
+      <c r="BM20" s="23"/>
+      <c r="BN20" s="23"/>
+      <c r="BO20" s="23"/>
+      <c r="EI20" s="22"/>
+      <c r="EJ20" s="23"/>
+      <c r="EK20" s="23"/>
+      <c r="EL20" s="23"/>
+    </row>
+    <row r="21" spans="2:142" ht="15.75" customHeight="1">
       <c r="F21" s="30"/>
       <c r="G21" s="20">
         <v>19</v>
@@ -6062,7 +6384,7 @@
       <c r="P21" s="21">
         <v>41040</v>
       </c>
-      <c r="Q21" s="38" t="s">
+      <c r="Q21" s="33" t="s">
         <v>200</v>
       </c>
       <c r="S21" s="20">
@@ -6075,7 +6397,7 @@
         <v>41040</v>
       </c>
       <c r="V21" s="21"/>
-      <c r="W21" s="38" t="s">
+      <c r="W21" s="33" t="s">
         <v>256</v>
       </c>
       <c r="Y21" s="20">
@@ -6088,7 +6410,7 @@
       <c r="AB21" s="21">
         <v>41040</v>
       </c>
-      <c r="AC21" s="38" t="s">
+      <c r="AC21" s="33" t="s">
         <v>262</v>
       </c>
       <c r="AE21" s="20">
@@ -6101,7 +6423,7 @@
       <c r="AH21" s="21">
         <v>41040</v>
       </c>
-      <c r="AI21" s="38" t="s">
+      <c r="AI21" s="33" t="s">
         <v>268</v>
       </c>
       <c r="AK21" s="23"/>
@@ -6138,12 +6460,12 @@
       <c r="AZ21" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="BG21" s="23"/>
-      <c r="BH21" s="23"/>
-      <c r="BI21" s="23"/>
-      <c r="BJ21" s="23"/>
-    </row>
-    <row r="22" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL21" s="23"/>
+      <c r="BM21" s="23"/>
+      <c r="BN21" s="23"/>
+      <c r="BO21" s="23"/>
+    </row>
+    <row r="22" spans="2:142" ht="15.75" customHeight="1">
       <c r="F22" s="30"/>
       <c r="G22" s="20">
         <v>20</v>
@@ -6249,12 +6571,12 @@
       <c r="AZ22" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="BG22" s="23"/>
-      <c r="BH22" s="23"/>
-      <c r="BI22" s="23"/>
-      <c r="BJ22" s="23"/>
-    </row>
-    <row r="23" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL22" s="23"/>
+      <c r="BM22" s="23"/>
+      <c r="BN22" s="23"/>
+      <c r="BO22" s="23"/>
+    </row>
+    <row r="23" spans="2:142" ht="15.75" customHeight="1">
       <c r="F23" s="30"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
@@ -6325,12 +6647,12 @@
       <c r="AR23" s="23"/>
       <c r="AS23" s="23"/>
       <c r="AT23" s="24"/>
-      <c r="BG23" s="23"/>
-      <c r="BH23" s="23"/>
-      <c r="BI23" s="23"/>
-      <c r="BJ23" s="23"/>
-    </row>
-    <row r="24" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL23" s="23"/>
+      <c r="BM23" s="23"/>
+      <c r="BN23" s="23"/>
+      <c r="BO23" s="23"/>
+    </row>
+    <row r="24" spans="2:142" ht="15.75" customHeight="1">
       <c r="F24" s="30"/>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
@@ -6401,12 +6723,12 @@
       <c r="AR24" s="23"/>
       <c r="AS24" s="23"/>
       <c r="AT24" s="24"/>
-      <c r="BG24" s="23"/>
-      <c r="BH24" s="23"/>
-      <c r="BI24" s="23"/>
-      <c r="BJ24" s="23"/>
-    </row>
-    <row r="25" spans="2:137" ht="15.75" customHeight="1">
+      <c r="BL24" s="23"/>
+      <c r="BM24" s="23"/>
+      <c r="BN24" s="23"/>
+      <c r="BO24" s="23"/>
+    </row>
+    <row r="25" spans="2:142" ht="15.75" customHeight="1">
       <c r="F25" s="30"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
@@ -6476,24 +6798,24 @@
       <c r="AQ25" s="23"/>
       <c r="AR25" s="23"/>
       <c r="AS25" s="23"/>
-      <c r="BG25" s="23"/>
-      <c r="BH25" s="23"/>
-      <c r="BI25" s="23"/>
-      <c r="BJ25" s="23"/>
-      <c r="BL25" s="22"/>
-      <c r="BM25" s="22"/>
-      <c r="BN25" s="22"/>
-      <c r="BO25" s="22"/>
-      <c r="CA25" s="22"/>
-      <c r="CB25" s="23"/>
-      <c r="CC25" s="23"/>
-      <c r="CD25" s="23"/>
+      <c r="BL25" s="23"/>
+      <c r="BM25" s="23"/>
+      <c r="BN25" s="23"/>
+      <c r="BO25" s="23"/>
+      <c r="BQ25" s="22"/>
+      <c r="BR25" s="22"/>
+      <c r="BS25" s="22"/>
+      <c r="BT25" s="22"/>
       <c r="CF25" s="22"/>
       <c r="CG25" s="23"/>
       <c r="CH25" s="23"/>
       <c r="CI25" s="23"/>
-    </row>
-    <row r="26" spans="2:137" ht="15.75" customHeight="1">
+      <c r="CK25" s="22"/>
+      <c r="CL25" s="23"/>
+      <c r="CM25" s="23"/>
+      <c r="CN25" s="23"/>
+    </row>
+    <row r="26" spans="2:142" ht="15.75" customHeight="1">
       <c r="F26" s="30"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
@@ -6564,18 +6886,14 @@
       <c r="AR26" s="23"/>
       <c r="AS26" s="23"/>
       <c r="AT26" s="24"/>
-      <c r="BG26" s="23"/>
-      <c r="BH26" s="23"/>
-      <c r="BI26" s="23"/>
-      <c r="BJ26" s="23"/>
-      <c r="BL26" s="22"/>
-      <c r="BM26" s="22"/>
-      <c r="BN26" s="22"/>
-      <c r="BO26" s="22"/>
+      <c r="BL26" s="23"/>
+      <c r="BM26" s="23"/>
+      <c r="BN26" s="23"/>
+      <c r="BO26" s="23"/>
       <c r="BQ26" s="22"/>
-      <c r="BR26" s="23"/>
-      <c r="BS26" s="23"/>
-      <c r="BT26" s="23"/>
+      <c r="BR26" s="22"/>
+      <c r="BS26" s="22"/>
+      <c r="BT26" s="22"/>
       <c r="BV26" s="22"/>
       <c r="BW26" s="23"/>
       <c r="BX26" s="23"/>
@@ -6588,8 +6906,12 @@
       <c r="CG26" s="23"/>
       <c r="CH26" s="23"/>
       <c r="CI26" s="23"/>
-    </row>
-    <row r="27" spans="2:137" ht="15.75" customHeight="1">
+      <c r="CK26" s="22"/>
+      <c r="CL26" s="23"/>
+      <c r="CM26" s="23"/>
+      <c r="CN26" s="23"/>
+    </row>
+    <row r="27" spans="2:142" ht="15.75" customHeight="1">
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
       <c r="D27" s="22"/>
@@ -6664,18 +6986,14 @@
       <c r="AR27" s="23"/>
       <c r="AS27" s="23"/>
       <c r="AT27" s="24"/>
-      <c r="BG27" s="23"/>
-      <c r="BH27" s="23"/>
-      <c r="BI27" s="23"/>
-      <c r="BJ27" s="23"/>
-      <c r="BL27" s="22"/>
-      <c r="BM27" s="22"/>
-      <c r="BN27" s="22"/>
-      <c r="BO27" s="22"/>
+      <c r="BL27" s="23"/>
+      <c r="BM27" s="23"/>
+      <c r="BN27" s="23"/>
+      <c r="BO27" s="23"/>
       <c r="BQ27" s="22"/>
-      <c r="BR27" s="23"/>
-      <c r="BS27" s="23"/>
-      <c r="BT27" s="23"/>
+      <c r="BR27" s="22"/>
+      <c r="BS27" s="22"/>
+      <c r="BT27" s="22"/>
       <c r="BV27" s="22"/>
       <c r="BW27" s="23"/>
       <c r="BX27" s="23"/>
@@ -6688,8 +7006,12 @@
       <c r="CG27" s="23"/>
       <c r="CH27" s="23"/>
       <c r="CI27" s="23"/>
-    </row>
-    <row r="28" spans="2:137" ht="15.75" customHeight="1">
+      <c r="CK27" s="22"/>
+      <c r="CL27" s="23"/>
+      <c r="CM27" s="23"/>
+      <c r="CN27" s="23"/>
+    </row>
+    <row r="28" spans="2:142" ht="15.75" customHeight="1">
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
       <c r="D28" s="22"/>
@@ -6768,18 +7090,18 @@
       <c r="BC28" s="23"/>
       <c r="BD28" s="23"/>
       <c r="BE28" s="23"/>
-      <c r="BG28" s="22"/>
-      <c r="BH28" s="22"/>
-      <c r="BI28" s="22"/>
-      <c r="BJ28" s="22"/>
+      <c r="BG28" s="23"/>
+      <c r="BH28" s="23"/>
+      <c r="BI28" s="23"/>
+      <c r="BJ28" s="23"/>
       <c r="BL28" s="22"/>
       <c r="BM28" s="22"/>
       <c r="BN28" s="22"/>
       <c r="BO28" s="22"/>
       <c r="BQ28" s="22"/>
-      <c r="BR28" s="23"/>
-      <c r="BS28" s="23"/>
-      <c r="BT28" s="23"/>
+      <c r="BR28" s="22"/>
+      <c r="BS28" s="22"/>
+      <c r="BT28" s="22"/>
       <c r="BV28" s="22"/>
       <c r="BW28" s="23"/>
       <c r="BX28" s="23"/>
@@ -6792,8 +7114,12 @@
       <c r="CG28" s="23"/>
       <c r="CH28" s="23"/>
       <c r="CI28" s="23"/>
-    </row>
-    <row r="29" spans="2:137" ht="15.75" customHeight="1">
+      <c r="CK28" s="22"/>
+      <c r="CL28" s="23"/>
+      <c r="CM28" s="23"/>
+      <c r="CN28" s="23"/>
+    </row>
+    <row r="29" spans="2:142" ht="15.75" customHeight="1">
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
@@ -6872,18 +7198,18 @@
       <c r="BC29" s="23"/>
       <c r="BD29" s="23"/>
       <c r="BE29" s="23"/>
-      <c r="BG29" s="22"/>
-      <c r="BH29" s="22"/>
-      <c r="BI29" s="22"/>
-      <c r="BJ29" s="22"/>
+      <c r="BG29" s="23"/>
+      <c r="BH29" s="23"/>
+      <c r="BI29" s="23"/>
+      <c r="BJ29" s="23"/>
       <c r="BL29" s="22"/>
       <c r="BM29" s="22"/>
       <c r="BN29" s="22"/>
       <c r="BO29" s="22"/>
       <c r="BQ29" s="22"/>
-      <c r="BR29" s="23"/>
-      <c r="BS29" s="23"/>
-      <c r="BT29" s="23"/>
+      <c r="BR29" s="22"/>
+      <c r="BS29" s="22"/>
+      <c r="BT29" s="22"/>
       <c r="BV29" s="22"/>
       <c r="BW29" s="23"/>
       <c r="BX29" s="23"/>
@@ -6896,8 +7222,12 @@
       <c r="CG29" s="23"/>
       <c r="CH29" s="23"/>
       <c r="CI29" s="23"/>
-    </row>
-    <row r="30" spans="2:137" ht="15.75" customHeight="1">
+      <c r="CK29" s="22"/>
+      <c r="CL29" s="23"/>
+      <c r="CM29" s="23"/>
+      <c r="CN29" s="23"/>
+    </row>
+    <row r="30" spans="2:142" ht="15.75" customHeight="1">
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
       <c r="D30" s="22"/>
@@ -6976,18 +7306,18 @@
       <c r="BC30" s="23"/>
       <c r="BD30" s="23"/>
       <c r="BE30" s="23"/>
-      <c r="BG30" s="22"/>
-      <c r="BH30" s="22"/>
-      <c r="BI30" s="22"/>
-      <c r="BJ30" s="22"/>
+      <c r="BG30" s="23"/>
+      <c r="BH30" s="23"/>
+      <c r="BI30" s="23"/>
+      <c r="BJ30" s="23"/>
       <c r="BL30" s="22"/>
       <c r="BM30" s="22"/>
       <c r="BN30" s="22"/>
       <c r="BO30" s="22"/>
       <c r="BQ30" s="22"/>
-      <c r="BR30" s="23"/>
-      <c r="BS30" s="23"/>
-      <c r="BT30" s="23"/>
+      <c r="BR30" s="22"/>
+      <c r="BS30" s="22"/>
+      <c r="BT30" s="22"/>
       <c r="BV30" s="22"/>
       <c r="BW30" s="23"/>
       <c r="BX30" s="23"/>
@@ -7000,8 +7330,12 @@
       <c r="CG30" s="23"/>
       <c r="CH30" s="23"/>
       <c r="CI30" s="23"/>
-    </row>
-    <row r="31" spans="2:137" ht="15.75" customHeight="1">
+      <c r="CK30" s="22"/>
+      <c r="CL30" s="23"/>
+      <c r="CM30" s="23"/>
+      <c r="CN30" s="23"/>
+    </row>
+    <row r="31" spans="2:142" ht="15.75" customHeight="1">
       <c r="G31" s="24"/>
       <c r="H31" s="24"/>
       <c r="I31" s="24"/>
@@ -7080,18 +7414,18 @@
       <c r="BC31" s="23"/>
       <c r="BD31" s="23"/>
       <c r="BE31" s="23"/>
-      <c r="BG31" s="22"/>
-      <c r="BH31" s="22"/>
-      <c r="BI31" s="22"/>
-      <c r="BJ31" s="22"/>
+      <c r="BG31" s="23"/>
+      <c r="BH31" s="23"/>
+      <c r="BI31" s="23"/>
+      <c r="BJ31" s="23"/>
       <c r="BL31" s="22"/>
       <c r="BM31" s="22"/>
       <c r="BN31" s="22"/>
       <c r="BO31" s="22"/>
       <c r="BQ31" s="22"/>
-      <c r="BR31" s="23"/>
-      <c r="BS31" s="23"/>
-      <c r="BT31" s="23"/>
+      <c r="BR31" s="22"/>
+      <c r="BS31" s="22"/>
+      <c r="BT31" s="22"/>
       <c r="BV31" s="22"/>
       <c r="BW31" s="23"/>
       <c r="BX31" s="23"/>
@@ -7104,8 +7438,12 @@
       <c r="CG31" s="23"/>
       <c r="CH31" s="23"/>
       <c r="CI31" s="23"/>
-    </row>
-    <row r="32" spans="2:137" ht="15.75" customHeight="1">
+      <c r="CK31" s="22"/>
+      <c r="CL31" s="23"/>
+      <c r="CM31" s="23"/>
+      <c r="CN31" s="23"/>
+    </row>
+    <row r="32" spans="2:142" ht="15.75" customHeight="1">
       <c r="G32" s="24"/>
       <c r="H32" s="24"/>
       <c r="I32" s="24"/>
@@ -7184,18 +7522,18 @@
       <c r="BC32" s="23"/>
       <c r="BD32" s="23"/>
       <c r="BE32" s="23"/>
-      <c r="BG32" s="17"/>
-      <c r="BH32" s="17"/>
-      <c r="BI32" s="17"/>
-      <c r="BJ32" s="17"/>
+      <c r="BG32" s="23"/>
+      <c r="BH32" s="23"/>
+      <c r="BI32" s="23"/>
+      <c r="BJ32" s="23"/>
       <c r="BL32" s="17"/>
       <c r="BM32" s="17"/>
       <c r="BN32" s="17"/>
       <c r="BO32" s="17"/>
-      <c r="BQ32" s="22"/>
-      <c r="BR32" s="23"/>
-      <c r="BS32" s="23"/>
-      <c r="BT32" s="23"/>
+      <c r="BQ32" s="17"/>
+      <c r="BR32" s="17"/>
+      <c r="BS32" s="17"/>
+      <c r="BT32" s="17"/>
       <c r="BV32" s="22"/>
       <c r="BW32" s="23"/>
       <c r="BX32" s="23"/>
@@ -7208,8 +7546,12 @@
       <c r="CG32" s="23"/>
       <c r="CH32" s="23"/>
       <c r="CI32" s="23"/>
-    </row>
-    <row r="33" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK32" s="22"/>
+      <c r="CL32" s="23"/>
+      <c r="CM32" s="23"/>
+      <c r="CN32" s="23"/>
+    </row>
+    <row r="33" spans="7:92" ht="15.75" customHeight="1">
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
@@ -7234,18 +7576,18 @@
       <c r="BC33" s="23"/>
       <c r="BD33" s="23"/>
       <c r="BE33" s="23"/>
-      <c r="BG33" s="17"/>
-      <c r="BH33" s="17"/>
-      <c r="BI33" s="17"/>
-      <c r="BJ33" s="17"/>
+      <c r="BG33" s="23"/>
+      <c r="BH33" s="23"/>
+      <c r="BI33" s="23"/>
+      <c r="BJ33" s="23"/>
       <c r="BL33" s="17"/>
       <c r="BM33" s="17"/>
       <c r="BN33" s="17"/>
       <c r="BO33" s="17"/>
-      <c r="BQ33" s="22"/>
-      <c r="BR33" s="23"/>
-      <c r="BS33" s="23"/>
-      <c r="BT33" s="23"/>
+      <c r="BQ33" s="17"/>
+      <c r="BR33" s="17"/>
+      <c r="BS33" s="17"/>
+      <c r="BT33" s="17"/>
       <c r="BV33" s="22"/>
       <c r="BW33" s="23"/>
       <c r="BX33" s="23"/>
@@ -7258,8 +7600,12 @@
       <c r="CG33" s="23"/>
       <c r="CH33" s="23"/>
       <c r="CI33" s="23"/>
-    </row>
-    <row r="34" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK33" s="22"/>
+      <c r="CL33" s="23"/>
+      <c r="CM33" s="23"/>
+      <c r="CN33" s="23"/>
+    </row>
+    <row r="34" spans="7:92" ht="15.75" customHeight="1">
       <c r="G34" s="24"/>
       <c r="H34" s="24"/>
       <c r="I34" s="24"/>
@@ -7284,18 +7630,18 @@
       <c r="BC34" s="23"/>
       <c r="BD34" s="23"/>
       <c r="BE34" s="23"/>
-      <c r="BG34" s="17"/>
-      <c r="BH34" s="17"/>
-      <c r="BI34" s="17"/>
-      <c r="BJ34" s="17"/>
+      <c r="BG34" s="23"/>
+      <c r="BH34" s="23"/>
+      <c r="BI34" s="23"/>
+      <c r="BJ34" s="23"/>
       <c r="BL34" s="17"/>
       <c r="BM34" s="17"/>
       <c r="BN34" s="17"/>
       <c r="BO34" s="17"/>
-      <c r="BQ34" s="22"/>
-      <c r="BR34" s="23"/>
-      <c r="BS34" s="23"/>
-      <c r="BT34" s="23"/>
+      <c r="BQ34" s="17"/>
+      <c r="BR34" s="17"/>
+      <c r="BS34" s="17"/>
+      <c r="BT34" s="17"/>
       <c r="BV34" s="22"/>
       <c r="BW34" s="23"/>
       <c r="BX34" s="23"/>
@@ -7308,8 +7654,12 @@
       <c r="CG34" s="23"/>
       <c r="CH34" s="23"/>
       <c r="CI34" s="23"/>
-    </row>
-    <row r="35" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK34" s="22"/>
+      <c r="CL34" s="23"/>
+      <c r="CM34" s="23"/>
+      <c r="CN34" s="23"/>
+    </row>
+    <row r="35" spans="7:92" ht="15.75" customHeight="1">
       <c r="G35" s="24"/>
       <c r="H35" s="24"/>
       <c r="I35" s="24"/>
@@ -7342,10 +7692,10 @@
       <c r="BM35" s="17"/>
       <c r="BN35" s="17"/>
       <c r="BO35" s="17"/>
-      <c r="BQ35" s="22"/>
-      <c r="BR35" s="23"/>
-      <c r="BS35" s="23"/>
-      <c r="BT35" s="23"/>
+      <c r="BQ35" s="17"/>
+      <c r="BR35" s="17"/>
+      <c r="BS35" s="17"/>
+      <c r="BT35" s="17"/>
       <c r="BV35" s="22"/>
       <c r="BW35" s="23"/>
       <c r="BX35" s="23"/>
@@ -7358,8 +7708,12 @@
       <c r="CG35" s="23"/>
       <c r="CH35" s="23"/>
       <c r="CI35" s="23"/>
-    </row>
-    <row r="36" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK35" s="22"/>
+      <c r="CL35" s="23"/>
+      <c r="CM35" s="23"/>
+      <c r="CN35" s="23"/>
+    </row>
+    <row r="36" spans="7:92" ht="15.75" customHeight="1">
       <c r="G36" s="24"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -7392,10 +7746,10 @@
       <c r="BM36" s="17"/>
       <c r="BN36" s="17"/>
       <c r="BO36" s="17"/>
-      <c r="BQ36" s="22"/>
-      <c r="BR36" s="23"/>
-      <c r="BS36" s="23"/>
-      <c r="BT36" s="23"/>
+      <c r="BQ36" s="17"/>
+      <c r="BR36" s="17"/>
+      <c r="BS36" s="17"/>
+      <c r="BT36" s="17"/>
       <c r="BV36" s="22"/>
       <c r="BW36" s="23"/>
       <c r="BX36" s="23"/>
@@ -7408,8 +7762,12 @@
       <c r="CG36" s="23"/>
       <c r="CH36" s="23"/>
       <c r="CI36" s="23"/>
-    </row>
-    <row r="37" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK36" s="22"/>
+      <c r="CL36" s="23"/>
+      <c r="CM36" s="23"/>
+      <c r="CN36" s="23"/>
+    </row>
+    <row r="37" spans="7:92" ht="15.75" customHeight="1">
       <c r="G37" s="24"/>
       <c r="H37" s="24"/>
       <c r="I37" s="24"/>
@@ -7458,8 +7816,12 @@
       <c r="CG37" s="17"/>
       <c r="CH37" s="17"/>
       <c r="CI37" s="17"/>
-    </row>
-    <row r="38" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK37" s="17"/>
+      <c r="CL37" s="17"/>
+      <c r="CM37" s="17"/>
+      <c r="CN37" s="17"/>
+    </row>
+    <row r="38" spans="7:92" ht="15.75" customHeight="1">
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
       <c r="I38" s="24"/>
@@ -7508,8 +7870,12 @@
       <c r="CG38" s="17"/>
       <c r="CH38" s="17"/>
       <c r="CI38" s="17"/>
-    </row>
-    <row r="39" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK38" s="17"/>
+      <c r="CL38" s="17"/>
+      <c r="CM38" s="17"/>
+      <c r="CN38" s="17"/>
+    </row>
+    <row r="39" spans="7:92" ht="15.75" customHeight="1">
       <c r="G39" s="24"/>
       <c r="H39" s="24"/>
       <c r="I39" s="24"/>
@@ -7558,8 +7924,12 @@
       <c r="CG39" s="17"/>
       <c r="CH39" s="17"/>
       <c r="CI39" s="17"/>
-    </row>
-    <row r="40" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK39" s="17"/>
+      <c r="CL39" s="17"/>
+      <c r="CM39" s="17"/>
+      <c r="CN39" s="17"/>
+    </row>
+    <row r="40" spans="7:92" ht="15.75" customHeight="1">
       <c r="G40" s="24"/>
       <c r="H40" s="24"/>
       <c r="I40" s="24"/>
@@ -7608,8 +7978,12 @@
       <c r="CG40" s="17"/>
       <c r="CH40" s="17"/>
       <c r="CI40" s="17"/>
-    </row>
-    <row r="41" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK40" s="17"/>
+      <c r="CL40" s="17"/>
+      <c r="CM40" s="17"/>
+      <c r="CN40" s="17"/>
+    </row>
+    <row r="41" spans="7:92" ht="15.75" customHeight="1">
       <c r="G41" s="24"/>
       <c r="H41" s="24"/>
       <c r="I41" s="24"/>
@@ -7658,8 +8032,12 @@
       <c r="CG41" s="17"/>
       <c r="CH41" s="17"/>
       <c r="CI41" s="17"/>
-    </row>
-    <row r="42" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK41" s="17"/>
+      <c r="CL41" s="17"/>
+      <c r="CM41" s="17"/>
+      <c r="CN41" s="17"/>
+    </row>
+    <row r="42" spans="7:92" ht="15.75" customHeight="1">
       <c r="G42" s="24"/>
       <c r="H42" s="24"/>
       <c r="I42" s="24"/>
@@ -7708,8 +8086,12 @@
       <c r="CG42" s="17"/>
       <c r="CH42" s="17"/>
       <c r="CI42" s="17"/>
-    </row>
-    <row r="43" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK42" s="17"/>
+      <c r="CL42" s="17"/>
+      <c r="CM42" s="17"/>
+      <c r="CN42" s="17"/>
+    </row>
+    <row r="43" spans="7:92" ht="15.75" customHeight="1">
       <c r="G43" s="24"/>
       <c r="H43" s="24"/>
       <c r="I43" s="24"/>
@@ -7758,8 +8140,12 @@
       <c r="CG43" s="17"/>
       <c r="CH43" s="17"/>
       <c r="CI43" s="17"/>
-    </row>
-    <row r="44" spans="7:87" ht="15.75" customHeight="1">
+      <c r="CK43" s="17"/>
+      <c r="CL43" s="17"/>
+      <c r="CM43" s="17"/>
+      <c r="CN43" s="17"/>
+    </row>
+    <row r="44" spans="7:92" ht="15.75" customHeight="1">
       <c r="G44" s="24"/>
       <c r="H44" s="24"/>
       <c r="I44" s="24"/>
@@ -7808,29 +8194,33 @@
       <c r="CG44" s="17"/>
       <c r="CH44" s="17"/>
       <c r="CI44" s="17"/>
-    </row>
-    <row r="45" spans="7:87" ht="13.5">
+      <c r="CK44" s="17"/>
+      <c r="CL44" s="17"/>
+      <c r="CM44" s="17"/>
+      <c r="CN44" s="17"/>
+    </row>
+    <row r="45" spans="7:92" ht="13.5">
       <c r="G45" s="24"/>
       <c r="H45" s="24"/>
       <c r="I45" s="24"/>
       <c r="J45" s="24"/>
       <c r="K45" s="24"/>
     </row>
-    <row r="46" spans="7:87" ht="13.5">
+    <row r="46" spans="7:92" ht="13.5">
       <c r="G46" s="24"/>
       <c r="H46" s="24"/>
       <c r="I46" s="24"/>
       <c r="J46" s="24"/>
       <c r="K46" s="24"/>
     </row>
-    <row r="47" spans="7:87" ht="13.5">
+    <row r="47" spans="7:92" ht="13.5">
       <c r="G47" s="24"/>
       <c r="H47" s="24"/>
       <c r="I47" s="24"/>
       <c r="J47" s="24"/>
       <c r="K47" s="24"/>
     </row>
-    <row r="48" spans="7:87" ht="15.75" customHeight="1">
+    <row r="48" spans="7:92" ht="15.75" customHeight="1">
       <c r="G48" s="24"/>
       <c r="H48" s="24"/>
       <c r="I48" s="24"/>
@@ -7952,29 +8342,29 @@
         <v>8</v>
       </c>
       <c r="K2" s="2"/>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="35"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="43"/>
       <c r="U2" s="2"/>
-      <c r="V2" s="33" t="s">
+      <c r="V2" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="35"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="42"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="43"/>
     </row>
     <row r="3" spans="2:30">
       <c r="B3" s="3">
@@ -8119,10 +8509,10 @@
       <c r="AD5" s="6"/>
     </row>
     <row r="6" spans="2:30">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="32"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="14">
         <f t="shared" ref="D6:J6" si="0">SUM(D3:D5)</f>
         <v>100</v>
@@ -8478,10 +8868,10 @@
       <c r="AD13" s="6"/>
     </row>
     <row r="14" spans="2:30">
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="32"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="14">
         <f t="shared" ref="D14:J14" si="1">SUM(D9:D13)</f>
         <v>150</v>
@@ -8596,10 +8986,10 @@
       </c>
       <c r="K16" s="2"/>
       <c r="U16" s="2"/>
-      <c r="V16" s="31" t="s">
+      <c r="V16" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W16" s="32"/>
+      <c r="W16" s="40"/>
       <c r="X16" s="15">
         <f t="shared" ref="X16:AD16" si="2">SUM(X4:X15)</f>
         <v>375</v>
@@ -8828,10 +9218,10 @@
       <c r="AD22" s="2"/>
     </row>
     <row r="23" spans="2:30">
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="32"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="14">
         <f t="shared" ref="D23:J23" si="3">SUM(D17:D22)</f>
         <v>160</v>
@@ -9261,10 +9651,10 @@
       <c r="AD35" s="2"/>
     </row>
     <row r="36" spans="2:30">
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="32"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="14">
         <f t="shared" ref="D36:J36" si="4">SUM(D26:D35)</f>
         <v>285</v>
@@ -9564,10 +9954,10 @@
       <c r="AD44" s="2"/>
     </row>
     <row r="45" spans="2:30">
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="32"/>
+      <c r="C45" s="40"/>
       <c r="D45" s="14">
         <f t="shared" ref="D45:J45" si="5">SUM(D39:D44)</f>
         <v>160</v>
@@ -9946,10 +10336,10 @@
       </c>
     </row>
     <row r="59" spans="2:30">
-      <c r="B59" s="31" t="s">
+      <c r="B59" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="32"/>
+      <c r="C59" s="40"/>
       <c r="D59" s="14">
         <f t="shared" ref="D59:J59" si="6">SUM(D49:D58)</f>
         <v>285</v>
@@ -10167,10 +10557,10 @@
       </c>
     </row>
     <row r="69" spans="2:10">
-      <c r="B69" s="31" t="s">
+      <c r="B69" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="32"/>
+      <c r="C69" s="40"/>
       <c r="D69" s="14">
         <f t="shared" ref="D69:J69" si="7">SUM(D62:D68)</f>
         <v>185</v>
@@ -10463,10 +10853,10 @@
       </c>
     </row>
     <row r="82" spans="2:10">
-      <c r="B82" s="31" t="s">
+      <c r="B82" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="C82" s="32"/>
+      <c r="C82" s="40"/>
       <c r="D82" s="14">
         <f t="shared" ref="D82:J82" si="8">SUM(D72:D81)</f>
         <v>300</v>
@@ -10715,10 +11105,10 @@
       </c>
     </row>
     <row r="93" spans="2:10">
-      <c r="B93" s="31" t="s">
+      <c r="B93" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="C93" s="32"/>
+      <c r="C93" s="40"/>
       <c r="D93" s="14">
         <f t="shared" ref="D93:J93" si="9">SUM(D85:D92)</f>
         <v>350</v>
